--- a/tool/package-generator/doc/03_結合テスト/テスト仕様書.xlsx
+++ b/tool/package-generator/doc/03_結合テスト/テスト仕様書.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\myrepo\project_management\tool\package-generator\doc\03_結合テスト\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{84FF84D0-0A8B-4900-884C-CD1CAFEFB40A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A9D79E7D-EABA-4B66-8523-5E5C2AC5ABB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="6120" windowWidth="23040" windowHeight="6120" xr2:uid="{9F4C83B4-138C-417D-8566-C89A6FA849EF}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F69F0D6D-B7B7-4642-875F-AC83FD4390BE}"/>
   </bookViews>
   <sheets>
     <sheet name="一覧" sheetId="1" r:id="rId1"/>
@@ -23,13 +23,13 @@
     <sheet name="2.7 環境設定（パッケージ定義）" sheetId="8" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2.1 実行（一括実行）'!$A$1:$F$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'2.2 実行（パッケージ作成）'!$A$1:$F$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'2.3 実行（パッケージ反映）'!$A$1:$F$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'2.4 ログ'!$A$1:$F$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'2.5 環境設定（共通）'!$A$1:$F$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'2.6 環境設定（グループ別）'!$A$1:$F$21</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'2.7 環境設定（パッケージ定義）'!$A$1:$F$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2.1 実行（一括実行）'!$A$1:$G$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'2.2 実行（パッケージ作成）'!$A$1:$G$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'2.3 実行（パッケージ反映）'!$A$1:$G$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'2.4 ログ'!$A$1:$G$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'2.5 環境設定（共通）'!$A$1:$G$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'2.6 環境設定（グループ別）'!$A$1:$G$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'2.7 環境設定（パッケージ定義）'!$A$1:$G$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">一覧!$A$1:$C$8</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="479" uniqueCount="172">
   <si>
     <t>通番</t>
   </si>
@@ -107,25 +107,34 @@
     <t>区分</t>
   </si>
   <si>
+    <t>入力値</t>
+  </si>
+  <si>
     <t>操作</t>
   </si>
   <si>
-    <t>期待結果</t>
+    <t>期待値</t>
   </si>
   <si>
     <t>参照</t>
   </si>
   <si>
-    <t>結果</t>
+    <t>実施結果</t>
   </si>
   <si>
     <t>正常系</t>
   </si>
   <si>
-    <t>パッケージのアップロードのチェックを外し、パッケージの作成だけにチェックを付けて、実行を押します。</t>
-  </si>
-  <si>
-    <t>パッケージの作成だけが実行され、パッケージのアップロードは実行されずスキップと表示されます。</t>
+    <t>対象のグループ：ok
+パッケージの作成：あり
+パッケージのアップロード：なし</t>
+  </si>
+  <si>
+    <t>実行を押します。</t>
+  </si>
+  <si>
+    <t>パッケージの作成の状態：成功または警告
+パッケージのアップロードの状態：スキップ</t>
   </si>
   <si>
     <t>画面設計 3.1、処理フロー 2.3</t>
@@ -134,64 +143,82 @@
     <t/>
   </si>
   <si>
-    <t>両方にチェックを付け、タイトルとフォルダを入力して、実行を押します。</t>
-  </si>
-  <si>
-    <t>パッケージが作成され、続けて zip ファイルがアップロードされます。状態に、それぞれの処理の成功が表示されます。</t>
+    <t>対象のグループ：ok
+パッケージの作成：あり
+パッケージのアップロード：あり</t>
+  </si>
+  <si>
+    <t>パッケージの作成の状態：成功
+パッケージのアップロードの状態：成功</t>
+  </si>
+  <si>
+    <t>対象のグループ：ok</t>
   </si>
   <si>
     <t>実行が終わったあと、ログ欄を確認します。</t>
   </si>
   <si>
-    <t>実行結果のログが表示されます。ログの出力先に実行ログが保存されます。</t>
+    <t>パッケージの作成の状態：成功または警告
+ログ欄：実行結果が表示される</t>
   </si>
   <si>
     <t>パッケージの作成の「開く」を押します。</t>
   </si>
   <si>
-    <t>作成したパッケージの出力先のフォルダが開きます。</t>
+    <t>開いた画面：作成したパッケージの出力先のフォルダ</t>
   </si>
   <si>
     <t>パッケージのアップロードの「開く」を押します。</t>
   </si>
   <si>
-    <t>対象の kintone アプリが開きます。</t>
+    <t>開いた画面：対象の kintone アプリ</t>
   </si>
   <si>
     <t>異常系</t>
   </si>
   <si>
-    <t>タイトルを空にして、パッケージのアップロードにチェックを付け、実行を押します。</t>
-  </si>
-  <si>
-    <t>「タイトル を設定してください。」と表示され、処理は実行されません。</t>
-  </si>
-  <si>
-    <t>フォルダを空にして、パッケージのアップロードにチェックを付け、実行を押します。</t>
-  </si>
-  <si>
-    <t>「フォルダ を設定してください。」と表示され、処理は実行されません。</t>
+    <t>タイトル：空
+フォルダ：空
+パッケージのアップロード：あり</t>
+  </si>
+  <si>
+    <t>メッセージ：「タイトル を設定してください。」
+処理：実行されない</t>
+  </si>
+  <si>
+    <t>タイトル：TestTitle
+フォルダ：空
+パッケージのアップロード：あり</t>
+  </si>
+  <si>
+    <t>メッセージ：「フォルダ を設定してください。」
+処理：実行されない</t>
   </si>
   <si>
     <t>8</t>
   </si>
   <si>
-    <t>異常のクライアント（ng）で、圧縮元のフォルダが存在しない状態で、両方にチェックを付けて実行を押します。</t>
-  </si>
-  <si>
-    <t>パッケージの作成は警告と表示されますが、後続のパッケージのアップロードは続けて実行されます。</t>
-  </si>
-  <si>
-    <t>異常のクライアント（ng）で、パッケージのアップロードだけにチェックを付けて、実行を押します。</t>
-  </si>
-  <si>
-    <t>パッケージのアップロードの状態に失敗と表示されます。</t>
-  </si>
-  <si>
-    <t>対象のグループを選び、実行を押します。</t>
-  </si>
-  <si>
-    <t>圧縮元のフォルダの内容から、シートごとの zip ファイルが、パッケージの出力先に作られます。「テンプレート」シートの zip ファイルは作られません。</t>
+    <t>対象のグループ：ng（圧縮元のフォルダがない）
+パッケージの作成：あり
+パッケージのアップロード：あり</t>
+  </si>
+  <si>
+    <t>パッケージの作成の状態：警告
+パッケージのアップロードの状態：成功、警告、失敗のいずれか
+後続の処理：実行される</t>
+  </si>
+  <si>
+    <t>対象のグループ：ng
+パッケージの作成：なし
+パッケージのアップロード：あり</t>
+  </si>
+  <si>
+    <t>パッケージのアップロードの状態：失敗</t>
+  </si>
+  <si>
+    <t>状態：成功
+シートごとの zip ファイル：パッケージの出力先に作られる
+「テンプレート」シートの zip ファイル：作られない</t>
   </si>
   <si>
     <t>画面設計 3.2、処理フロー 2.1</t>
@@ -200,208 +227,261 @@
     <t>実行が完了したあと、開くを押します。</t>
   </si>
   <si>
-    <t>パッケージの出力先のフォルダが開きます。</t>
+    <t>開いた画面：パッケージの出力先のフォルダ</t>
   </si>
   <si>
     <t>実行が完了したあと、状態とログを確認します。</t>
   </si>
   <si>
-    <t>状態に成功と表示され、ログ欄に実行結果が表示されます。</t>
-  </si>
-  <si>
-    <t>警告のクライアント（warn）で、実行を押します。</t>
-  </si>
-  <si>
-    <t>状態に警告と表示されます。</t>
-  </si>
-  <si>
-    <t>異常のクライアント（ng）で、実行を押します。</t>
-  </si>
-  <si>
-    <t>状態に警告と表示され、実行ログに記録されます。</t>
-  </si>
-  <si>
-    <t>正常のクライアント（ok）で、パッケージ定義ファイルを削除してから実行を押します。</t>
-  </si>
-  <si>
-    <t>状態に失敗と表示され、実行ログに記録されます。</t>
-  </si>
-  <si>
-    <t>ファイル1に zip ファイルを指定し、タイトルを入力して、実行を押します。</t>
-  </si>
-  <si>
-    <t>kintone のアプリに、入力したタイトルのレコードが作成され、zip ファイルが添付されます。</t>
+    <t>状態：成功
+ログ欄：実行結果が表示される</t>
+  </si>
+  <si>
+    <t>対象のグループ：warn</t>
+  </si>
+  <si>
+    <t>状態：警告</t>
+  </si>
+  <si>
+    <t>対象のグループ：ng</t>
+  </si>
+  <si>
+    <t>状態：警告
+実行ログ：記録される</t>
+  </si>
+  <si>
+    <t>対象のグループ：ok
+パッケージ定義ファイル：削除（clients\ok.xlsx）</t>
+  </si>
+  <si>
+    <t>状態：失敗
+実行ログ：記録される</t>
+  </si>
+  <si>
+    <t>対象のグループ：ok
+タイトル：TestTitle
+ファイル1：generated\ok\コースA.zip</t>
+  </si>
+  <si>
+    <t>状態：成功
+kintone のレコード：作成され、zip ファイルが添付される</t>
   </si>
   <si>
     <t>画面設計 3.3、処理フロー 2.2</t>
   </si>
   <si>
-    <t>フォルダを指定し、フォルダの中の zip ファイルが対象になるように、実行を押します。</t>
-  </si>
-  <si>
-    <t>フォルダの中の zip ファイルが、すべて添付されます。</t>
-  </si>
-  <si>
-    <t>1 で作成したレコードと同じタイトルで、もう一度実行を押します。</t>
-  </si>
-  <si>
-    <t>既存のレコードが更新され、新しいレコードは作られません。ログに、レコードを更新したと表示されます。</t>
-  </si>
-  <si>
-    <t>説明を入力して、実行を押します。</t>
-  </si>
-  <si>
-    <t>レコードの説明欄に、入力した説明が入ります。</t>
-  </si>
-  <si>
-    <t>フォルダの「クリア（フォルダ）」を押します。</t>
-  </si>
-  <si>
-    <t>フォルダの入力が消えます。</t>
+    <t>対象のグループ：ok
+タイトル：TestTitle
+フォルダ：入力なし（画面に入っている値のまま）</t>
+  </si>
+  <si>
+    <t>状態：成功
+zip ファイル：フォルダの中のものがすべて添付される</t>
+  </si>
+  <si>
+    <t>状態：成功
+既存のレコード：更新される
+新しいレコード：作られない</t>
+  </si>
+  <si>
+    <t>対象のグループ：ok
+タイトル：TestTitle
+ファイル1：generated\ok\コースA.zip
+説明：テスト説明</t>
+  </si>
+  <si>
+    <t>状態：成功
+レコードの説明：入力した説明が入る</t>
+  </si>
+  <si>
+    <t>対象のグループ：ok
+フォルダ：generated\ok</t>
+  </si>
+  <si>
+    <t>「クリア（フォルダ）」を押します。</t>
+  </si>
+  <si>
+    <t>フォルダ：空</t>
   </si>
   <si>
     <t>画面設計 3.3</t>
   </si>
   <si>
-    <t>ファイル1の「クリア（ファイル1）」を押します。</t>
-  </si>
-  <si>
-    <t>ファイル1の入力が消えます。ファイル2とファイル3の入力は残ります。</t>
-  </si>
-  <si>
-    <t>タイトルを空にして、実行を押します。</t>
-  </si>
-  <si>
-    <t>「タイトルを入力してください」と表示され、実行されません。</t>
-  </si>
-  <si>
-    <t>zip ファイルを 1 つも指定せず、実行を押します。</t>
-  </si>
-  <si>
-    <t>「zipファイルを1つ以上指定してください」と表示され、実行されません。</t>
+    <t>対象のグループ：ok
+ファイル1：generated\ok\コースA.zip</t>
+  </si>
+  <si>
+    <t>「クリア（ファイル1）」を押します。</t>
+  </si>
+  <si>
+    <t>ファイル1：空
+ファイル2・ファイル3：変わらない</t>
+  </si>
+  <si>
+    <t>タイトル：空</t>
+  </si>
+  <si>
+    <t>メッセージ：「タイトルを入力してください」
+処理：実行されない</t>
+  </si>
+  <si>
+    <t>タイトル：TestTitle
+ファイル1：空
+ファイル2：空
+ファイル3：空</t>
+  </si>
+  <si>
+    <t>メッセージ：「zipファイルを1つ以上指定してください」
+処理：実行されない</t>
   </si>
   <si>
     <t>10</t>
   </si>
   <si>
-    <t>同じ名前の zip ファイルを、ファイル1とフォルダの中の両方に指定して、実行を押します。</t>
-  </si>
-  <si>
-    <t>「同じ名前のzipファイルがあります：」と、重複したファイル名が表示され、実行されません。</t>
-  </si>
-  <si>
-    <t>異常のクライアント（ng）で、タイトルを入力し、zipのない場所をフォルダに指定して、実行を押します。</t>
-  </si>
-  <si>
-    <t>状態に失敗と表示されます。</t>
-  </si>
-  <si>
-    <t>ログの出力先にログファイルがない状態で、すべて削除を押します。</t>
-  </si>
-  <si>
-    <t>「削除対象のログファイルがありません。」と表示されます。</t>
+    <t>メッセージ：「同じ名前のzipファイルがあります：」、重複したファイル名が表示される</t>
+  </si>
+  <si>
+    <t>対象のグループ：ng
+タイトル：TestTitle
+ファイル1：generated\ng\コースA.zip</t>
+  </si>
+  <si>
+    <t>状態：失敗</t>
+  </si>
+  <si>
+    <t>画面設計 3.3、処理フロー 2.3</t>
+  </si>
+  <si>
+    <t>ログファイルがない状態で、すべて削除を押します。</t>
+  </si>
+  <si>
+    <t>メッセージ：「削除対象のログファイルがありません。」</t>
   </si>
   <si>
     <t>画面設計 3.4、処理フロー 2.4</t>
   </si>
   <si>
-    <t>ログファイルがある状態で、すべて削除を押し、確認で「いいえ」を選びます。</t>
-  </si>
-  <si>
-    <t>何も削除されず、ログファイルは残ります。</t>
-  </si>
-  <si>
-    <t>ログファイルがある状態で、すべて削除を押し、確認で「はい」を選びます。</t>
-  </si>
-  <si>
-    <t>ログの出力先のログファイルがすべて削除されます。</t>
-  </si>
-  <si>
-    <t>対象のグループで「すべて」を選んだあと、「ok」を選びます。</t>
-  </si>
-  <si>
-    <t>「すべて」では両方のログが表示され、「ok」を選ぶと ok のログだけが表示されます。</t>
+    <t>確認：いいえ</t>
+  </si>
+  <si>
+    <t>ログファイルがある状態で、すべて削除を押します。</t>
+  </si>
+  <si>
+    <t>ログファイル：残る</t>
+  </si>
+  <si>
+    <t>確認：はい</t>
+  </si>
+  <si>
+    <t>ログファイル：すべて削除される</t>
+  </si>
+  <si>
+    <t>対象のグループ：すべて、ok、ng</t>
+  </si>
+  <si>
+    <t>対象のグループを選びます。</t>
+  </si>
+  <si>
+    <t>表示されるログ：「すべて」を選ぶと ok と ng の両方、「ok」を選ぶと ok のログだけ、「ng」を選ぶと ng のログだけ</t>
   </si>
   <si>
     <t>画面設計 3.4</t>
   </si>
   <si>
-    <t>対象のグループで「すべて」を選びます。</t>
-  </si>
-  <si>
-    <t>グループで絞り込まれず、すべてのグループのログが表示されます。</t>
+    <t>対象のグループ：すべて</t>
+  </si>
+  <si>
+    <t>表示されるログ：すべてのグループのログ</t>
   </si>
   <si>
     <t>処理のラジオボタンを切り替えます。</t>
   </si>
   <si>
-    <t>選んだ処理のログだけが表示されます。</t>
-  </si>
-  <si>
-    <t>ログの出力先を変えて、保存を押します。</t>
-  </si>
-  <si>
-    <t>変えた値が保存され、画面の表示が保存後の内容に更新されます。結果がボタンの横に表示されます。</t>
+    <t>表示されるログ：選んだ処理のログだけ（ok と ng の両方）</t>
+  </si>
+  <si>
+    <t>ログの出力先：%BASE_PATH%logs2</t>
+  </si>
+  <si>
+    <t>保存を押します。</t>
+  </si>
+  <si>
+    <t>設定ファイル（bats\common.bat）：logs2 を含む値が保存される
+ボタンの横の状態：完了
+画面の表示：保存後の内容に更新</t>
   </si>
   <si>
     <t>画面設計 3.5、処理フロー 2.5</t>
   </si>
   <si>
-    <t>ログの出力先を変えたあと、再読込を押します。</t>
-  </si>
-  <si>
-    <t>保存されている値で入力欄が表示し直され、変えた内容は消えます。</t>
+    <t>ログの出力先：tmp</t>
+  </si>
+  <si>
+    <t>再読込を押します。</t>
+  </si>
+  <si>
+    <t>ログの出力先：%BASE_PATH%logs（保存されている値）
+変えた内容：消える</t>
   </si>
   <si>
     <t>画面設計 3.5、処理フロー 2.6</t>
   </si>
   <si>
-    <t>新規作成を押し、新しい名前を入力します。</t>
-  </si>
-  <si>
-    <t>名前が対象のグループの一覧に追加され、選ばれます。</t>
+    <t>新しい名前：PkgNew</t>
+  </si>
+  <si>
+    <t>新規作成を押します。</t>
+  </si>
+  <si>
+    <t>一覧：PkgNew が追加され、選ばれる</t>
   </si>
   <si>
     <t>画面設計 3.6、処理フロー 2.7</t>
   </si>
   <si>
-    <t>新規作成で追加したグループを選び、保存を押します。</t>
-  </si>
-  <si>
-    <t>設定ファイルと、パッケージ定義ファイルが雛形からコピーされ、入力した内容が保存されます。</t>
+    <t>ファイル：clients\PkgNew.bat と clients\PkgNew.xlsx が作られる
+入力した内容：保存される</t>
   </si>
   <si>
     <t>画面設計 3.6、処理フロー 2.9</t>
   </si>
   <si>
-    <t>保存済みのグループを選び、コピーを押して、新しい名前を入力します。</t>
-  </si>
-  <si>
-    <t>新しいグループが一覧に 1 つだけ追加され、選ばれます。画面の値は、コピー元と同じになります。</t>
+    <t>対象のグループ：CopySrc
+新しい名前：PkgCopy</t>
+  </si>
+  <si>
+    <t>コピーを押します。</t>
+  </si>
+  <si>
+    <t>一覧：PkgCopy が追加され、選ばれる
+ファイル：clients\PkgCopy.bat と clients\PkgCopy.xlsx が作られる
+画面の値：コピー元と同じ</t>
   </si>
   <si>
     <t>画面設計 3.6、処理フロー 2.8</t>
   </si>
   <si>
-    <t>3 のあとで、clients フォルダを確認します。</t>
-  </si>
-  <si>
-    <t>新しいグループの設定ファイルと Excel ファイルが作られます。コピー元のファイルは変わりません。</t>
-  </si>
-  <si>
-    <t>3 のあとで、パッケージ作成のパッケージ定義ファイルと、パッケージの出力先の欄を確認します。</t>
-  </si>
-  <si>
-    <t>欄の値の中のグループ名が、新しいグループの名前になっています。</t>
-  </si>
-  <si>
-    <t>入力欄の値を変えて、保存を押します。</t>
-  </si>
-  <si>
-    <t>値が設定ファイルに保存され、画面の表示が保存後の内容に更新されます。</t>
-  </si>
-  <si>
-    <t>入力欄の値を変えたあと、再読込を押します。</t>
+    <t>ファイル：clients\PkgCopy.bat と clients\PkgCopy.xlsx が作られる
+clients\CopySrc.bat の内容：generated\CopySrc を含む（変わらない）</t>
+  </si>
+  <si>
+    <t>ファイル：clients\PkgCopy.bat の内容：generated\PkgCopy を含む（パッケージの出力先の名前が新しいグループの名前になる）</t>
+  </si>
+  <si>
+    <t>対象のグループ：CopySrc
+サブドメイン：saved</t>
+  </si>
+  <si>
+    <t>設定ファイル（clients\CopySrc.bat）：saved を含む値が保存される
+ボタンの横の状態：完了</t>
+  </si>
+  <si>
+    <t>対象のグループ：CopySrc
+サブドメイン：tmp</t>
+  </si>
+  <si>
+    <t>サブドメイン：univ-kyousai-{x}（保存されている値）
+変えた内容：消える</t>
   </si>
   <si>
     <t>画面設計 3.6、処理フロー 2.10</t>
@@ -410,40 +490,52 @@
     <t>開く（対象のグループ）を押します。</t>
   </si>
   <si>
-    <t>対象のグループの Excel ファイル（パッケージ定義ファイル）が開きます。</t>
+    <t>開いた画面：対象のグループの Excel ファイル（ok.xlsx）</t>
   </si>
   <si>
     <t>画面設計 3.6</t>
   </si>
   <si>
-    <t>正しい接続情報を入力して、テスト接続（kintone接続）を押します。</t>
-  </si>
-  <si>
-    <t>ボタンの横の状態に成功と表示されます。</t>
+    <t>対象のグループ：ok、入力なし（保存されている接続情報）</t>
+  </si>
+  <si>
+    <t>テスト接続（kintone接続）を押します。</t>
+  </si>
+  <si>
+    <t>ボタンの横の状態：成功</t>
   </si>
   <si>
     <t>画面設計 3.6、処理フロー 2.11</t>
   </si>
   <si>
-    <t>存在するアプリIDを入力して、テスト接続（ファイル管理）を押します。</t>
+    <t>対象のグループ：ok、入力なし（保存されている対象アプリID）</t>
+  </si>
+  <si>
+    <t>テスト接続（ファイル管理）を押します。</t>
   </si>
   <si>
     <t>画面設計 3.6、処理フロー 2.12</t>
   </si>
   <si>
-    <t>パッケージ作成の対象のシートに値を入れて、保存を押し、画面を選び直します。</t>
-  </si>
-  <si>
-    <t>入力した値が残っています。</t>
+    <t>対象のグループ：ok
+対象のシート：1,2</t>
+  </si>
+  <si>
+    <t>保存を押し、対象のグループを選び直します。</t>
+  </si>
+  <si>
+    <t>設定ファイル（clients\ok.bat）：GenerateSheetsInclude=1,2 が保存される
+対象のシート：1,2 が残る</t>
   </si>
   <si>
     <t>12</t>
   </si>
   <si>
-    <t>新規作成を押し、既存のグループと同じ名前を入力します。</t>
-  </si>
-  <si>
-    <t>「「（入力した名前）」は既に存在します。」と表示され、グループは追加されません。</t>
+    <t>新しい名前：ok（既存のグループ名）</t>
+  </si>
+  <si>
+    <t>メッセージ：「（入力した名前）は既に存在します。」
+一覧：追加されない</t>
   </si>
   <si>
     <t>13</t>
@@ -452,82 +544,97 @@
     <t>新規作成を押したあと、キャンセルを押します。</t>
   </si>
   <si>
-    <t>一覧は変わりません。</t>
+    <t>ファイル：clients\PkgCancel.bat が作られない
+一覧：変わらない</t>
   </si>
   <si>
     <t>14</t>
   </si>
   <si>
-    <t>新規作成直後の、まだ保存していないグループを選び、コピーを押します。</t>
-  </si>
-  <si>
-    <t>「コピー元のグループが存在しません」と表示され、コピーは行われません。</t>
+    <t>新しい名前：PkgUnsaved</t>
+  </si>
+  <si>
+    <t>メッセージ：「コピー元のグループが存在しません」
+ファイル：clients\PkgUnsaved.bat が作られない</t>
   </si>
   <si>
     <t>15</t>
   </si>
   <si>
-    <t>コピーを押し、既存のグループと同じ名前を入力します。</t>
-  </si>
-  <si>
-    <t>「「（入力した名前）」は既に存在します。」と表示され、コピーは行われません。</t>
+    <t>対象のグループ：CopySrc
+新しい名前：CopySrc</t>
+  </si>
+  <si>
+    <t>メッセージ：「（入力した名前）は既に存在します。」
+コピー：行われない</t>
   </si>
   <si>
     <t>16</t>
   </si>
   <si>
-    <t>kintone接続のサブドメインを空にして、テスト接続（kintone接続）を押します。</t>
-  </si>
-  <si>
-    <t>ボタンの横の状態に失敗と表示され、接続は行われません。</t>
+    <t>対象のグループ：ok
+サブドメイン：空</t>
+  </si>
+  <si>
+    <t>ボタンの横の状態：失敗
+接続：行われない</t>
   </si>
   <si>
     <t>17</t>
   </si>
   <si>
-    <t>誤ったパスワードを入力して、テスト接続（kintone接続）を押します。</t>
-  </si>
-  <si>
-    <t>ボタンの横の状態に失敗と表示されます。</t>
+    <t>対象のグループ：ok
+パスワード：wrong-password</t>
+  </si>
+  <si>
+    <t>ボタンの横の状態：失敗</t>
   </si>
   <si>
     <t>18</t>
   </si>
   <si>
-    <t>ファイル管理の対象アプリIDを空にして、テスト接続（ファイル管理）を押します。</t>
+    <t>対象のグループ：ok
+対象アプリID：空</t>
   </si>
   <si>
     <t>19</t>
   </si>
   <si>
-    <t>存在しないアプリIDを入力して、テスト接続（ファイル管理）を押します。</t>
-  </si>
-  <si>
-    <t>異常のクライアント（ng）を選び、誤ったパスワードを入力して、テスト接続（kintone接続）を押します。</t>
-  </si>
-  <si>
-    <t>「テンプレート」シートの 2 行目以降が、圧縮元のフォルダの内容で作り直されます。状態に成功と表示され、ログが表示されます。</t>
+    <t>対象のグループ：ok
+対象アプリID：99999999</t>
+  </si>
+  <si>
+    <t>対象のグループ：ng
+パスワード：wrong-password</t>
+  </si>
+  <si>
+    <t>状態：成功
+テンプレートシートの 2 行目以降：圧縮元のフォルダの内容で作り直される
+ログ：表示される</t>
   </si>
   <si>
     <t>画面設計 3.7、処理フロー 2.13</t>
   </si>
   <si>
-    <t>「テンプレート」シートの 2 行目に任意の値を入れて保存したあと、実行を押します。</t>
-  </si>
-  <si>
-    <t>2 行目に入れた値は消去され、圧縮元のフォルダの内容に置き換わります。</t>
+    <t>対象のグループ：ok
+テンプレート（A2）：MARKER_ROW2（準備で書き込み）</t>
+  </si>
+  <si>
+    <t>状態：成功
+テンプレートシートの 2 行目：消去される</t>
   </si>
   <si>
     <t>画面設計 3.7、処理フロー 2.13、処理フロー 3</t>
   </si>
   <si>
-    <t>更新されたパッケージ定義ファイルが開きます。</t>
+    <t>開いた画面：更新されたパッケージ定義ファイル（ok.xlsx）</t>
   </si>
   <si>
     <t>画面設計 3.7</t>
   </si>
   <si>
-    <t>対象のグループのパッケージ定義ファイルを Excel で開いたままにして、実行を押します。</t>
+    <t>対象のグループ：ok
+パッケージ定義ファイル：Excel で開いたまま</t>
   </si>
 </sst>
 </file>
@@ -926,7 +1033,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5568FBDE-3C19-4954-AE07-B850A83315FC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8FF4B9FB-990D-459A-9A77-EEDE0EB88ABD}">
   <dimension ref="A1:C8"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -1024,26 +1131,27 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C8" xr:uid="{5568FBDE-3C19-4954-AE07-B850A83315FC}"/>
+  <autoFilter ref="A1:C8" xr:uid="{8FF4B9FB-990D-459A-9A77-EEDE0EB88ABD}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FBBCD830-D48C-433C-9AEC-FB0908D4D61C}">
-  <dimension ref="A1:F10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6FFF4174-91F5-4E15-B1D0-FEB7DB5692D3}">
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="8.69921875" customWidth="1"/>
     <col min="2" max="2" width="10.69921875" customWidth="1"/>
-    <col min="3" max="3" width="45.69921875" customWidth="1"/>
-    <col min="4" max="4" width="60.69921875" customWidth="1"/>
-    <col min="5" max="5" width="28.69921875" customWidth="1"/>
-    <col min="6" max="6" width="10.69921875" customWidth="1"/>
+    <col min="3" max="3" width="50.69921875" customWidth="1"/>
+    <col min="4" max="4" width="45.69921875" customWidth="1"/>
+    <col min="5" max="5" width="75.69921875" customWidth="1"/>
+    <col min="6" max="6" width="28.69921875" customWidth="1"/>
+    <col min="7" max="7" width="12.69921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1062,208 +1170,239 @@
       <c r="F1" s="1" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" ht="234" x14ac:dyDescent="0.45">
+      <c r="G1" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="180" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="252" x14ac:dyDescent="0.45">
+        <v>30</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="180" x14ac:dyDescent="0.45">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="F3" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="162" x14ac:dyDescent="0.45">
+      <c r="G3" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="162" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="108" x14ac:dyDescent="0.45">
+        <v>30</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="108" x14ac:dyDescent="0.45">
       <c r="A5" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>34</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="108" x14ac:dyDescent="0.45">
+        <v>30</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="108" x14ac:dyDescent="0.45">
       <c r="A6" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="180" x14ac:dyDescent="0.45">
+        <v>30</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="162" x14ac:dyDescent="0.45">
       <c r="A7" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="180" x14ac:dyDescent="0.45">
+        <v>30</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="162" x14ac:dyDescent="0.45">
       <c r="A8" s="2" t="s">
         <v>18</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="270" x14ac:dyDescent="0.45">
+      <c r="A9" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="E8" s="2" t="s">
+      <c r="C9" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="F8" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="234" x14ac:dyDescent="0.45">
-      <c r="A9" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>45</v>
-      </c>
       <c r="E9" s="2" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="234" x14ac:dyDescent="0.45">
+        <v>30</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="180" x14ac:dyDescent="0.45">
       <c r="A10" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>31</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F10" xr:uid="{FBBCD830-D48C-433C-9AEC-FB0908D4D61C}"/>
+  <autoFilter ref="A1:G10" xr:uid="{6FFF4174-91F5-4E15-B1D0-FEB7DB5692D3}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D86D6F7-4D16-42FE-9A4D-1877006BCDE0}">
-  <dimension ref="A1:F7"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D5AA3FF-5737-448C-87CB-6953374C3070}">
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="8.69921875" customWidth="1"/>
     <col min="2" max="2" width="10.69921875" customWidth="1"/>
-    <col min="3" max="3" width="45.69921875" customWidth="1"/>
-    <col min="4" max="4" width="60.69921875" customWidth="1"/>
-    <col min="5" max="5" width="28.69921875" customWidth="1"/>
-    <col min="6" max="6" width="10.69921875" customWidth="1"/>
+    <col min="3" max="3" width="50.69921875" customWidth="1"/>
+    <col min="4" max="4" width="45.69921875" customWidth="1"/>
+    <col min="5" max="5" width="75.69921875" customWidth="1"/>
+    <col min="6" max="6" width="28.69921875" customWidth="1"/>
+    <col min="7" max="7" width="12.69921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1282,148 +1421,170 @@
       <c r="F1" s="1" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" ht="324" x14ac:dyDescent="0.45">
+      <c r="G1" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="270" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="90" x14ac:dyDescent="0.45">
+        <v>52</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="90" x14ac:dyDescent="0.45">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="D3" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="F3" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="E3" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="126" x14ac:dyDescent="0.45">
+      <c r="G3" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="108" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="126" x14ac:dyDescent="0.45">
+        <v>52</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="72" x14ac:dyDescent="0.45">
       <c r="A5" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="108" x14ac:dyDescent="0.45">
+        <v>52</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="90" x14ac:dyDescent="0.45">
       <c r="A6" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>58</v>
+        <v>28</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="180" x14ac:dyDescent="0.45">
+        <v>52</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="180" x14ac:dyDescent="0.45">
       <c r="A7" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>60</v>
+        <v>28</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>29</v>
+        <v>52</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>31</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F7" xr:uid="{0D86D6F7-4D16-42FE-9A4D-1877006BCDE0}"/>
+  <autoFilter ref="A1:G7" xr:uid="{8D5AA3FF-5737-448C-87CB-6953374C3070}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2DB8DFD5-96AE-4917-B761-340C46DD21EF}">
-  <dimension ref="A1:F12"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3FEFF57A-18BB-41CB-9A64-BE88581CD6BE}">
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="8.69921875" customWidth="1"/>
     <col min="2" max="2" width="10.69921875" customWidth="1"/>
-    <col min="3" max="3" width="45.69921875" customWidth="1"/>
-    <col min="4" max="4" width="60.69921875" customWidth="1"/>
-    <col min="5" max="5" width="28.69921875" customWidth="1"/>
-    <col min="6" max="6" width="10.69921875" customWidth="1"/>
+    <col min="3" max="3" width="50.69921875" customWidth="1"/>
+    <col min="4" max="4" width="45.69921875" customWidth="1"/>
+    <col min="5" max="5" width="75.69921875" customWidth="1"/>
+    <col min="6" max="6" width="28.69921875" customWidth="1"/>
+    <col min="7" max="7" width="12.69921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1442,248 +1603,285 @@
       <c r="F1" s="1" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" ht="198" x14ac:dyDescent="0.45">
+      <c r="G1" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="198" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>62</v>
+        <v>28</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="198" x14ac:dyDescent="0.45">
+        <v>65</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="216" x14ac:dyDescent="0.45">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D3" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="F3" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="E3" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="234" x14ac:dyDescent="0.45">
+      <c r="G3" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="198" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>67</v>
+        <v>28</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="108" x14ac:dyDescent="0.45">
+        <v>65</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="234" x14ac:dyDescent="0.45">
       <c r="A5" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>69</v>
+        <v>28</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="108" x14ac:dyDescent="0.45">
+        <v>65</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="126" x14ac:dyDescent="0.45">
       <c r="A6" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="162" x14ac:dyDescent="0.45">
+        <v>74</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="144" x14ac:dyDescent="0.45">
       <c r="A7" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D7" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="F7" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="E7" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="90" x14ac:dyDescent="0.45">
+      <c r="G7" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="90" x14ac:dyDescent="0.45">
       <c r="A8" s="2" t="s">
         <v>18</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="144" x14ac:dyDescent="0.45">
+        <v>74</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="162" x14ac:dyDescent="0.45">
       <c r="A9" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>76</v>
+        <v>28</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>63</v>
+        <v>79</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="162" x14ac:dyDescent="0.45">
+        <v>65</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="180" x14ac:dyDescent="0.45">
       <c r="A10" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>78</v>
+        <v>28</v>
       </c>
       <c r="E10" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="198" x14ac:dyDescent="0.45">
+      <c r="A11" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="F10" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="216" x14ac:dyDescent="0.45">
-      <c r="A11" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>80</v>
-      </c>
       <c r="D11" s="2" t="s">
-        <v>81</v>
+        <v>28</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>63</v>
+        <v>83</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="216" x14ac:dyDescent="0.45">
+        <v>65</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="198" x14ac:dyDescent="0.45">
       <c r="A12" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>83</v>
+        <v>28</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>28</v>
+        <v>85</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>29</v>
+        <v>86</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>31</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F12" xr:uid="{2DB8DFD5-96AE-4917-B761-340C46DD21EF}"/>
+  <autoFilter ref="A1:G12" xr:uid="{3FEFF57A-18BB-41CB-9A64-BE88581CD6BE}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A8EFD9D-1AAF-434A-85C9-992F8EF953D2}">
-  <dimension ref="A1:F7"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1301CEB6-1811-492F-93C6-7F26D4B04289}">
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="8.69921875" customWidth="1"/>
     <col min="2" max="2" width="10.69921875" customWidth="1"/>
-    <col min="3" max="3" width="45.69921875" customWidth="1"/>
-    <col min="4" max="4" width="60.69921875" customWidth="1"/>
-    <col min="5" max="5" width="28.69921875" customWidth="1"/>
-    <col min="6" max="6" width="10.69921875" customWidth="1"/>
+    <col min="3" max="3" width="50.69921875" customWidth="1"/>
+    <col min="4" max="4" width="45.69921875" customWidth="1"/>
+    <col min="5" max="5" width="75.69921875" customWidth="1"/>
+    <col min="6" max="6" width="28.69921875" customWidth="1"/>
+    <col min="7" max="7" width="12.69921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1702,148 +1900,170 @@
       <c r="F1" s="1" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" ht="144" x14ac:dyDescent="0.45">
+      <c r="G1" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="126" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>84</v>
+        <v>31</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="180" x14ac:dyDescent="0.45">
+        <v>89</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="126" x14ac:dyDescent="0.45">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="162" x14ac:dyDescent="0.45">
+        <v>89</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="126" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="198" x14ac:dyDescent="0.45">
+      <c r="G4" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="270" x14ac:dyDescent="0.45">
       <c r="A5" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="144" x14ac:dyDescent="0.45">
+        <v>98</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="90" x14ac:dyDescent="0.45">
       <c r="A6" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="90" x14ac:dyDescent="0.45">
+        <v>98</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="126" x14ac:dyDescent="0.45">
       <c r="A7" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>96</v>
+        <v>34</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>29</v>
+        <v>98</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>31</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F7" xr:uid="{1A8EFD9D-1AAF-434A-85C9-992F8EF953D2}"/>
+  <autoFilter ref="A1:G7" xr:uid="{1301CEB6-1811-492F-93C6-7F26D4B04289}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{378C703A-CB68-41CC-8C56-A063906C65D2}">
-  <dimension ref="A1:F3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{821A0272-3AC1-49F3-A1C0-39770D1CE2CE}">
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="8.69921875" customWidth="1"/>
     <col min="2" max="2" width="10.69921875" customWidth="1"/>
-    <col min="3" max="3" width="45.69921875" customWidth="1"/>
-    <col min="4" max="4" width="60.69921875" customWidth="1"/>
-    <col min="5" max="5" width="28.69921875" customWidth="1"/>
-    <col min="6" max="6" width="10.69921875" customWidth="1"/>
+    <col min="3" max="3" width="50.69921875" customWidth="1"/>
+    <col min="4" max="4" width="45.69921875" customWidth="1"/>
+    <col min="5" max="5" width="75.69921875" customWidth="1"/>
+    <col min="6" max="6" width="28.69921875" customWidth="1"/>
+    <col min="7" max="7" width="12.69921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1862,68 +2082,78 @@
       <c r="F1" s="1" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" ht="216" x14ac:dyDescent="0.45">
+      <c r="G1" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="288" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="144" x14ac:dyDescent="0.45">
+        <v>106</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="198" x14ac:dyDescent="0.45">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>29</v>
+        <v>110</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>31</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F3" xr:uid="{378C703A-CB68-41CC-8C56-A063906C65D2}"/>
+  <autoFilter ref="A1:G3" xr:uid="{821A0272-3AC1-49F3-A1C0-39770D1CE2CE}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19FF59F2-99B3-42AF-A3DF-DC1BF5EF9057}">
-  <dimension ref="A1:F21"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30FDBC43-3B6B-4C99-9B50-6CF255973405}">
+  <dimension ref="A1:G21"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="8.69921875" customWidth="1"/>
     <col min="2" max="2" width="10.69921875" customWidth="1"/>
-    <col min="3" max="3" width="45.69921875" customWidth="1"/>
-    <col min="4" max="4" width="60.69921875" customWidth="1"/>
-    <col min="5" max="5" width="28.69921875" customWidth="1"/>
-    <col min="6" max="6" width="10.69921875" customWidth="1"/>
+    <col min="3" max="3" width="50.69921875" customWidth="1"/>
+    <col min="4" max="4" width="45.69921875" customWidth="1"/>
+    <col min="5" max="5" width="75.69921875" customWidth="1"/>
+    <col min="6" max="6" width="28.69921875" customWidth="1"/>
+    <col min="7" max="7" width="12.69921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1942,428 +2172,492 @@
       <c r="F1" s="1" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" ht="126" x14ac:dyDescent="0.45">
+      <c r="G1" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="90" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="216" x14ac:dyDescent="0.45">
+        <v>114</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="216" x14ac:dyDescent="0.45">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="216" x14ac:dyDescent="0.45">
+        <v>116</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="324" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="216" x14ac:dyDescent="0.45">
+        <v>120</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="324" x14ac:dyDescent="0.45">
       <c r="A5" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="216" x14ac:dyDescent="0.45">
+        <v>120</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="306" x14ac:dyDescent="0.45">
       <c r="A6" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="162" x14ac:dyDescent="0.45">
+        <v>120</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="216" x14ac:dyDescent="0.45">
       <c r="A7" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>118</v>
+        <v>104</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>109</v>
+        <v>124</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="144" x14ac:dyDescent="0.45">
+        <v>116</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="180" x14ac:dyDescent="0.45">
       <c r="A8" s="2" t="s">
         <v>18</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="162" x14ac:dyDescent="0.45">
+        <v>127</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="144" x14ac:dyDescent="0.45">
       <c r="A9" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>121</v>
+        <v>34</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="162" x14ac:dyDescent="0.45">
+        <v>130</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="126" x14ac:dyDescent="0.45">
       <c r="A10" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="162" x14ac:dyDescent="0.45">
+        <v>134</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="144" x14ac:dyDescent="0.45">
       <c r="A11" s="2" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>125</v>
+        <v>136</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="180" x14ac:dyDescent="0.45">
+        <v>137</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="252" x14ac:dyDescent="0.45">
       <c r="A12" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>109</v>
+        <v>140</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="198" x14ac:dyDescent="0.45">
+        <v>116</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="180" x14ac:dyDescent="0.45">
       <c r="A13" s="2" t="s">
-        <v>131</v>
+        <v>141</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C13" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="144" x14ac:dyDescent="0.45">
+      <c r="A14" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="234" x14ac:dyDescent="0.45">
+      <c r="A15" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="180" x14ac:dyDescent="0.45">
+      <c r="A16" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="108" x14ac:dyDescent="0.45">
+      <c r="A17" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="D17" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="D13" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="108" x14ac:dyDescent="0.45">
-      <c r="A14" s="2" t="s">
+      <c r="E17" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="F17" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="B14" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="D14" s="2" t="s">
+      <c r="G17" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="126" x14ac:dyDescent="0.45">
+      <c r="A18" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="90" x14ac:dyDescent="0.45">
+      <c r="A19" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="D19" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="E14" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="180" x14ac:dyDescent="0.45">
-      <c r="A15" s="2" t="s">
+      <c r="E19" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="F19" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" ht="198" x14ac:dyDescent="0.45">
-      <c r="A16" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" ht="180" x14ac:dyDescent="0.45">
-      <c r="A17" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" ht="162" x14ac:dyDescent="0.45">
-      <c r="A18" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" ht="180" x14ac:dyDescent="0.45">
-      <c r="A19" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" ht="162" x14ac:dyDescent="0.45">
+      <c r="G19" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="108" x14ac:dyDescent="0.45">
       <c r="A20" s="2" t="s">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>148</v>
+        <v>136</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>128</v>
+        <v>158</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" ht="234" x14ac:dyDescent="0.45">
+        <v>137</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="126" x14ac:dyDescent="0.45">
       <c r="A21" s="2" t="s">
         <v>17</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>148</v>
+        <v>132</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>126</v>
+        <v>158</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>29</v>
+        <v>134</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>31</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F21" xr:uid="{19FF59F2-99B3-42AF-A3DF-DC1BF5EF9057}"/>
+  <autoFilter ref="A1:G21" xr:uid="{30FDBC43-3B6B-4C99-9B50-6CF255973405}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6CB9599A-C935-4778-BE93-F533CDA75244}">
-  <dimension ref="A1:F5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE88AF5E-B95B-45EB-B4E1-F6A99777299A}">
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="8.69921875" customWidth="1"/>
     <col min="2" max="2" width="10.69921875" customWidth="1"/>
-    <col min="3" max="3" width="45.69921875" customWidth="1"/>
-    <col min="4" max="4" width="60.69921875" customWidth="1"/>
-    <col min="5" max="5" width="28.69921875" customWidth="1"/>
-    <col min="6" max="6" width="10.69921875" customWidth="1"/>
+    <col min="3" max="3" width="50.69921875" customWidth="1"/>
+    <col min="4" max="4" width="45.69921875" customWidth="1"/>
+    <col min="5" max="5" width="75.69921875" customWidth="1"/>
+    <col min="6" max="6" width="28.69921875" customWidth="1"/>
+    <col min="7" max="7" width="12.69921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2382,89 +2676,104 @@
       <c r="F1" s="1" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" ht="288" x14ac:dyDescent="0.45">
+      <c r="G1" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="234" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>154</v>
+        <v>28</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="180" x14ac:dyDescent="0.45">
+        <v>165</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="198" x14ac:dyDescent="0.45">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>157</v>
+        <v>28</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="108" x14ac:dyDescent="0.45">
+        <v>168</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="144" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>159</v>
+        <v>53</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="198" x14ac:dyDescent="0.45">
+        <v>170</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="162" x14ac:dyDescent="0.45">
       <c r="A5" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>60</v>
+        <v>28</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>158</v>
+        <v>62</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>29</v>
+        <v>168</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>31</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F5" xr:uid="{6CB9599A-C935-4778-BE93-F533CDA75244}"/>
+  <autoFilter ref="A1:G5" xr:uid="{AE88AF5E-B95B-45EB-B4E1-F6A99777299A}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/tool/package-generator/doc/03_結合テスト/テスト仕様書.xlsx
+++ b/tool/package-generator/doc/03_結合テスト/テスト仕様書.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\myrepo\project_management\tool\package-generator\doc\03_結合テスト\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A9D79E7D-EABA-4B66-8523-5E5C2AC5ABB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4DAD7A06-F234-4060-A1A0-A6BC85E8DDEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F69F0D6D-B7B7-4642-875F-AC83FD4390BE}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{4971C1B8-85C2-4425-8B28-13C5BBA0ED00}"/>
   </bookViews>
   <sheets>
     <sheet name="一覧" sheetId="1" r:id="rId1"/>
@@ -23,12 +23,12 @@
     <sheet name="2.7 環境設定（パッケージ定義）" sheetId="8" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2.1 実行（一括実行）'!$A$1:$G$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'2.2 実行（パッケージ作成）'!$A$1:$G$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'2.3 実行（パッケージ反映）'!$A$1:$G$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'2.4 ログ'!$A$1:$G$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'2.5 環境設定（共通）'!$A$1:$G$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'2.6 環境設定（グループ別）'!$A$1:$G$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2.1 実行（一括実行）'!$A$1:$G$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'2.2 実行（パッケージ作成）'!$A$1:$G$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'2.3 実行（パッケージ反映）'!$A$1:$G$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'2.4 ログ'!$A$1:$G$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'2.5 環境設定（共通）'!$A$1:$G$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'2.6 環境設定（グループ別）'!$A$1:$G$38</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'2.7 環境設定（パッケージ定義）'!$A$1:$G$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">一覧!$A$1:$C$8</definedName>
   </definedNames>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="479" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="598" uniqueCount="255">
   <si>
     <t>通番</t>
   </si>
@@ -77,7 +77,7 @@
     <t>実行（パッケージ反映）</t>
   </si>
   <si>
-    <t>11</t>
+    <t>13</t>
   </si>
   <si>
     <t>4</t>
@@ -86,6 +86,9 @@
     <t>ログ</t>
   </si>
   <si>
+    <t>7</t>
+  </si>
+  <si>
     <t>5</t>
   </si>
   <si>
@@ -95,10 +98,7 @@
     <t>環境設定（グループ別）</t>
   </si>
   <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>7</t>
+    <t>37</t>
   </si>
   <si>
     <t>環境設定（パッケージ定義）</t>
@@ -127,17 +127,20 @@
   <si>
     <t>対象のグループ：ok
 パッケージの作成：あり
-パッケージのアップロード：なし</t>
-  </si>
-  <si>
-    <t>実行を押します。</t>
-  </si>
-  <si>
-    <t>パッケージの作成の状態：成功または警告
-パッケージのアップロードの状態：スキップ</t>
-  </si>
-  <si>
-    <t>画面設計 3.1、処理フロー 2.3</t>
+パッケージのアップロード：なし
+設定ファイル：ok.bat</t>
+  </si>
+  <si>
+    <t>「対象のグループ」を設定した後で、「実行」を押します。</t>
+  </si>
+  <si>
+    <t>状態（パッケージの作成）：成功または警告
+状態（パッケージのアップロード）：スキップ
+状態：成功または警告</t>
+  </si>
+  <si>
+    <t>画面設計：3.1
+処理フロー：2.1</t>
   </si>
   <si>
     <t/>
@@ -145,54 +148,55 @@
   <si>
     <t>対象のグループ：ok
 パッケージの作成：あり
-パッケージのアップロード：あり</t>
-  </si>
-  <si>
-    <t>パッケージの作成の状態：成功
-パッケージのアップロードの状態：成功</t>
-  </si>
-  <si>
-    <t>対象のグループ：ok</t>
-  </si>
-  <si>
-    <t>実行が終わったあと、ログ欄を確認します。</t>
-  </si>
-  <si>
-    <t>パッケージの作成の状態：成功または警告
-ログ欄：実行結果が表示される</t>
-  </si>
-  <si>
-    <t>パッケージの作成の「開く」を押します。</t>
-  </si>
-  <si>
-    <t>開いた画面：作成したパッケージの出力先のフォルダ</t>
-  </si>
-  <si>
-    <t>パッケージのアップロードの「開く」を押します。</t>
-  </si>
-  <si>
-    <t>開いた画面：対象の kintone アプリ</t>
+パッケージのアップロード：あり
+設定ファイル：ok.bat</t>
+  </si>
+  <si>
+    <t>「対象のグループ」を設定した後で、「パッケージのアップロード」にチェックを入れて、「実行」を押します。</t>
+  </si>
+  <si>
+    <t>状態（パッケージの作成）：成功
+状態（パッケージのアップロード）：成功
+状態：成功または警告</t>
+  </si>
+  <si>
+    <t>「対象のグループ」を設定した後で、「実行」を押した後で、「開く（パッケージの作成）」を押します。</t>
+  </si>
+  <si>
+    <t>開く（パッケージの作成）：作成したパッケージの出力先のフォルダ
+状態（パッケージの作成）：成功または警告
+状態：成功または警告</t>
+  </si>
+  <si>
+    <t>「対象のグループ」を設定した後で、「実行」を押した後で、「開く（パッケージのアップロード）」を押します。</t>
+  </si>
+  <si>
+    <t>開いた画面：ファイル管理</t>
   </si>
   <si>
     <t>異常系</t>
   </si>
   <si>
-    <t>タイトル：空
+    <t>対象のグループ：ng
+タイトル：空
 フォルダ：空
-パッケージのアップロード：あり</t>
-  </si>
-  <si>
-    <t>メッセージ：「タイトル を設定してください。」
-処理：実行されない</t>
-  </si>
-  <si>
-    <t>タイトル：TestTitle
+パッケージの作成：あり
+パッケージのアップロード：あり
+設定ファイル：ng.bat</t>
+  </si>
+  <si>
+    <t>メッセージ：「タイトル を設定してください。」</t>
+  </si>
+  <si>
+    <t>対象のグループ：ng
+タイトル：TestTitle
 フォルダ：空
-パッケージのアップロード：あり</t>
-  </si>
-  <si>
-    <t>メッセージ：「フォルダ を設定してください。」
-処理：実行されない</t>
+パッケージの作成：あり
+パッケージのアップロード：あり
+設定ファイル：ng.bat</t>
+  </si>
+  <si>
+    <t>メッセージ：「フォルダ を設定してください。」</t>
   </si>
   <si>
     <t>8</t>
@@ -200,441 +204,804 @@
   <si>
     <t>対象のグループ：ng（圧縮元のフォルダがない）
 パッケージの作成：あり
-パッケージのアップロード：あり</t>
-  </si>
-  <si>
-    <t>パッケージの作成の状態：警告
-パッケージのアップロードの状態：成功、警告、失敗のいずれか
-後続の処理：実行される</t>
+パッケージのアップロード：あり
+設定ファイル：ng.bat</t>
+  </si>
+  <si>
+    <t>状態（パッケージの作成）：警告
+状態（パッケージのアップロード）：失敗
+状態：失敗</t>
   </si>
   <si>
     <t>対象のグループ：ng
 パッケージの作成：なし
-パッケージのアップロード：あり</t>
-  </si>
-  <si>
-    <t>パッケージのアップロードの状態：失敗</t>
+パッケージのアップロード：あり
+設定ファイル：ng.bat</t>
+  </si>
+  <si>
+    <t>「対象のグループ」を設定した後で、「パッケージの作成」のチェックを外して、「パッケージのアップロード」にチェックを入れて、「実行」を押します。</t>
+  </si>
+  <si>
+    <t>状態（パッケージのアップロード）：失敗
+状態：失敗</t>
+  </si>
+  <si>
+    <t>対象のグループ：ok
+設定ファイル：ok.bat
+圧縮元ファイル：sample.txt</t>
   </si>
   <si>
     <t>状態：成功
-シートごとの zip ファイル：パッケージの出力先に作られる
-「テンプレート」シートの zip ファイル：作られない</t>
-  </si>
-  <si>
-    <t>画面設計 3.2、処理フロー 2.1</t>
-  </si>
-  <si>
-    <t>実行が完了したあと、開くを押します。</t>
+パッケージの出力先（ok）：作られる</t>
+  </si>
+  <si>
+    <t>画面設計：3.2
+処理フロー：2.2</t>
+  </si>
+  <si>
+    <t>対象のグループ：ok
+設定ファイル：ok.bat</t>
+  </si>
+  <si>
+    <t>「対象のグループ」を設定した後で、「実行」を押した後で、「開く」を押します。</t>
   </si>
   <si>
     <t>開いた画面：パッケージの出力先のフォルダ</t>
   </si>
   <si>
-    <t>実行が完了したあと、状態とログを確認します。</t>
+    <t>対象のグループ：warn</t>
+  </si>
+  <si>
+    <t>状態：警告</t>
+  </si>
+  <si>
+    <t>対象のグループ：ng（圧縮元のフォルダがない）
+設定ファイル：ng.bat</t>
+  </si>
+  <si>
+    <t>対象のグループ：ok
+パッケージ定義ファイル：削除（ok.xlsx）
+設定ファイル：ok.bat</t>
+  </si>
+  <si>
+    <t>状態：失敗</t>
+  </si>
+  <si>
+    <t>対象のグループ：ok
+タイトル：TestTitle
+ファイル1：コースA.zip
+設定ファイル：ok.bat</t>
+  </si>
+  <si>
+    <t>「実行（パッケージ作成）」を実行し、「実行（パッケージ反映）」で「対象のグループ」を設定し、「クリア（フォルダ）」を押した後で、「タイトル」と「ファイル1」を設定した後で、「実行」を押します。</t>
   </si>
   <si>
     <t>状態：成功
-ログ欄：実行結果が表示される</t>
-  </si>
-  <si>
-    <t>対象のグループ：warn</t>
-  </si>
-  <si>
-    <t>状態：警告</t>
-  </si>
-  <si>
-    <t>対象のグループ：ng</t>
-  </si>
-  <si>
-    <t>状態：警告
-実行ログ：記録される</t>
-  </si>
-  <si>
-    <t>対象のグループ：ok
-パッケージ定義ファイル：削除（clients\ok.xlsx）</t>
-  </si>
-  <si>
-    <t>状態：失敗
-実行ログ：記録される</t>
+ログ：レコードIDが出力される</t>
+  </si>
+  <si>
+    <t>画面設計：3.3
+処理フロー：2.3</t>
   </si>
   <si>
     <t>対象のグループ：ok
 タイトル：TestTitle
-ファイル1：generated\ok\コースA.zip</t>
-  </si>
-  <si>
-    <t>状態：成功
-kintone のレコード：作成され、zip ファイルが添付される</t>
-  </si>
-  <si>
-    <t>画面設計 3.3、処理フロー 2.2</t>
-  </si>
-  <si>
-    <t>対象のグループ：ok
-タイトル：TestTitle
-フォルダ：入力なし（画面に入っている値のまま）</t>
-  </si>
-  <si>
-    <t>状態：成功
-zip ファイル：フォルダの中のものがすべて添付される</t>
+フォルダ：入力なし（画面に入っている値のまま）
+設定ファイル：ok.bat</t>
+  </si>
+  <si>
+    <t>「実行（パッケージ作成）」を実行し、「実行（パッケージ反映）」で「対象のグループ」と「タイトル」を設定した後で、「実行」を押します。</t>
+  </si>
+  <si>
+    <t>「実行（パッケージ作成）」を実行し、「実行（パッケージ反映）」で「対象のグループ」を設定し、「クリア（フォルダ）」を押した後で、「タイトル」と「ファイル1」を設定した後で、「実行」を押した後で、「実行」を押します。</t>
   </si>
   <si>
     <t>状態：成功
 既存のレコード：更新される
-新しいレコード：作られない</t>
+ログ：「同じタイトルのレコードを更新しました: レコードID（数字）」</t>
   </si>
   <si>
     <t>対象のグループ：ok
 タイトル：TestTitle
-ファイル1：generated\ok\コースA.zip
-説明：テスト説明</t>
+ファイル1：コースA.zip
+説明：テスト説明
+設定ファイル：ok.bat</t>
+  </si>
+  <si>
+    <t>「実行（パッケージ作成）」を実行し、「実行（パッケージ反映）」で「対象のグループ」を設定し、「クリア（フォルダ）」を押した後で、「タイトル」と「ファイル1」と「説明」を設定した後で、「実行」を押します。</t>
   </si>
   <si>
     <t>状態：成功
-レコードの説明：入力した説明が入る</t>
-  </si>
-  <si>
-    <t>対象のグループ：ok
-フォルダ：generated\ok</t>
-  </si>
-  <si>
-    <t>「クリア（フォルダ）」を押します。</t>
+ログ：入力した説明が入る</t>
+  </si>
+  <si>
+    <t>「実行（パッケージ作成）」を実行し、「実行（パッケージ反映）」で「対象のグループ」を設定し、「クリア（フォルダ）」を押します。</t>
   </si>
   <si>
     <t>フォルダ：空</t>
   </si>
   <si>
-    <t>画面設計 3.3</t>
-  </si>
-  <si>
-    <t>対象のグループ：ok
-ファイル1：generated\ok\コースA.zip</t>
-  </si>
-  <si>
-    <t>「クリア（ファイル1）」を押します。</t>
-  </si>
-  <si>
-    <t>ファイル1：空
-ファイル2・ファイル3：変わらない</t>
-  </si>
-  <si>
-    <t>タイトル：空</t>
-  </si>
-  <si>
-    <t>メッセージ：「タイトルを入力してください」
-処理：実行されない</t>
-  </si>
-  <si>
-    <t>タイトル：TestTitle
+    <t>画面設計：3.3</t>
+  </si>
+  <si>
+    <t>対象のグループ：ok
+ファイル1：コースA.zip
+設定ファイル：ok.bat</t>
+  </si>
+  <si>
+    <t>「実行（パッケージ作成）」を実行し、「実行（パッケージ反映）」で「対象のグループ」と「ファイル1」を設定した後で、「クリア（ファイル1）」を押します。</t>
+  </si>
+  <si>
+    <t>ファイル1：空</t>
+  </si>
+  <si>
+    <t>対象のグループ：ok
+ファイル2：コースA.zip
+設定ファイル：ok.bat</t>
+  </si>
+  <si>
+    <t>「実行（パッケージ作成）」を実行し、「実行（パッケージ反映）」で「対象のグループ」と「ファイル2」を設定した後で、「クリア（ファイル2）」を押します。</t>
+  </si>
+  <si>
+    <t>ファイル2：空</t>
+  </si>
+  <si>
+    <t>対象のグループ：ok
+ファイル3：コースA.zip
+設定ファイル：ok.bat</t>
+  </si>
+  <si>
+    <t>「実行（パッケージ作成）」を実行し、「実行（パッケージ反映）」で「対象のグループ」と「ファイル3」を設定した後で、「クリア（ファイル3）」を押します。</t>
+  </si>
+  <si>
+    <t>ファイル3：空</t>
+  </si>
+  <si>
+    <t>「実行（パッケージ反映）」で「対象のグループ」を設定した後で、「開く」を押します。</t>
+  </si>
+  <si>
+    <t>開いた画面：ファイル管理（未確認）</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>対象のグループ：ng
+タイトル：空
+設定ファイル：ng.bat</t>
+  </si>
+  <si>
+    <t>メッセージ：「タイトルを入力してください」</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>対象のグループ：ng
+タイトル：TestTitle
+フォルダ：空
 ファイル1：空
 ファイル2：空
-ファイル3：空</t>
-  </si>
-  <si>
-    <t>メッセージ：「zipファイルを1つ以上指定してください」
-処理：実行されない</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>メッセージ：「同じ名前のzipファイルがあります：」、重複したファイル名が表示される</t>
+ファイル3：空
+設定ファイル：ng.bat</t>
+  </si>
+  <si>
+    <t>「対象のグループ」と「タイトル」を設定した後で、「実行」を押します。</t>
+  </si>
+  <si>
+    <t>メッセージ：「zipファイルを1つ以上指定してください」</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>「実行（パッケージ作成）」を実行し、「実行（パッケージ反映）」で「対象のグループ」を設定し、「タイトル」と「ファイル1」を設定した後で、「実行」を押します。</t>
+  </si>
+  <si>
+    <t>メッセージ：「同じ名前のzipファイルがあります」</t>
   </si>
   <si>
     <t>対象のグループ：ng
 タイトル：TestTitle
-ファイル1：generated\ng\コースA.zip</t>
-  </si>
-  <si>
-    <t>状態：失敗</t>
-  </si>
-  <si>
-    <t>画面設計 3.3、処理フロー 2.3</t>
-  </si>
-  <si>
-    <t>ログファイルがない状態で、すべて削除を押します。</t>
+ファイル1：コースA.zip
+設定ファイル：ng.bat</t>
+  </si>
+  <si>
+    <t>「実行（パッケージ作成）」を実行し、「実行（パッケージ反映）」で「対象のグループ」と「タイトル」と「ファイル1」を設定した後で、「実行」を押します。</t>
+  </si>
+  <si>
+    <t>対象のグループ：すべて
+確認：いいえ
+処理：パッケージの作成</t>
+  </si>
+  <si>
+    <t>「対象のグループ」を設定した後で、ログのファイルがある状態で、「すべて削除」を押し、確認で「いいえ」を押します。</t>
+  </si>
+  <si>
+    <t>確認ダイアログ：ログファイルを削除します
+ログ：残る</t>
+  </si>
+  <si>
+    <t>画面設計：3.4
+処理フロー：2.4</t>
+  </si>
+  <si>
+    <t>対象のグループ：すべて
+確認：はい
+処理：パッケージの作成</t>
+  </si>
+  <si>
+    <t>「対象のグループ」を設定した後で、ログのファイルがある状態で、「すべて削除」を押し、確認で「はい」を押します。</t>
+  </si>
+  <si>
+    <t>確認ダイアログ：ログファイルを削除します
+ログ：すべて削除される</t>
+  </si>
+  <si>
+    <t>対象のグループ：すべて、ok
+処理：パッケージの作成</t>
+  </si>
+  <si>
+    <t>「対象のグループ」を切り替えます。</t>
+  </si>
+  <si>
+    <t>表示されるログ：「すべて」を選ぶと ok と ng の両方、「ok」を選ぶと ok のログだけ</t>
+  </si>
+  <si>
+    <t>画面設計：3.4</t>
+  </si>
+  <si>
+    <t>対象のグループ：すべて
+処理：パッケージの作成</t>
+  </si>
+  <si>
+    <t>「対象のグループ」を設定した後で、「処理」のラジオボタンを「パッケージの作成」、「パッケージのアップロード」、「パッケージの作成」の順に切り替えます。</t>
+  </si>
+  <si>
+    <t>表示されるログ：パッケージの作成のログだけ（ok と ng の両方）</t>
+  </si>
+  <si>
+    <t>「対象のグループ」を設定した後で、ログのファイルがない状態で、「すべて削除」を押します。</t>
   </si>
   <si>
     <t>メッセージ：「削除対象のログファイルがありません。」</t>
   </si>
   <si>
-    <t>画面設計 3.4、処理フロー 2.4</t>
-  </si>
-  <si>
-    <t>確認：いいえ</t>
-  </si>
-  <si>
-    <t>ログファイルがある状態で、すべて削除を押します。</t>
-  </si>
-  <si>
-    <t>ログファイル：残る</t>
-  </si>
-  <si>
-    <t>確認：はい</t>
-  </si>
-  <si>
-    <t>ログファイル：すべて削除される</t>
-  </si>
-  <si>
-    <t>対象のグループ：すべて、ok、ng</t>
-  </si>
-  <si>
-    <t>対象のグループを選びます。</t>
-  </si>
-  <si>
-    <t>表示されるログ：「すべて」を選ぶと ok と ng の両方、「ok」を選ぶと ok のログだけ、「ng」を選ぶと ng のログだけ</t>
-  </si>
-  <si>
-    <t>画面設計 3.4</t>
-  </si>
-  <si>
-    <t>対象のグループ：すべて</t>
-  </si>
-  <si>
-    <t>表示されるログ：すべてのグループのログ</t>
-  </si>
-  <si>
-    <t>処理のラジオボタンを切り替えます。</t>
-  </si>
-  <si>
-    <t>表示されるログ：選んだ処理のログだけ（ok と ng の両方）</t>
-  </si>
-  <si>
-    <t>ログの出力先：%BASE_PATH%logs2</t>
-  </si>
-  <si>
-    <t>保存を押します。</t>
-  </si>
-  <si>
-    <t>設定ファイル（bats\common.bat）：logs2 を含む値が保存される
-ボタンの横の状態：完了
-画面の表示：保存後の内容に更新</t>
-  </si>
-  <si>
-    <t>画面設計 3.5、処理フロー 2.5</t>
-  </si>
-  <si>
-    <t>ログの出力先：tmp</t>
-  </si>
-  <si>
-    <t>再読込を押します。</t>
-  </si>
-  <si>
-    <t>ログの出力先：%BASE_PATH%logs（保存されている値）
-変えた内容：消える</t>
-  </si>
-  <si>
-    <t>画面設計 3.5、処理フロー 2.6</t>
-  </si>
-  <si>
-    <t>新しい名前：PkgNew</t>
-  </si>
-  <si>
-    <t>新規作成を押します。</t>
-  </si>
-  <si>
-    <t>一覧：PkgNew が追加され、選ばれる</t>
-  </si>
-  <si>
-    <t>画面設計 3.6、処理フロー 2.7</t>
-  </si>
-  <si>
-    <t>ファイル：clients\PkgNew.bat と clients\PkgNew.xlsx が作られる
-入力した内容：保存される</t>
-  </si>
-  <si>
-    <t>画面設計 3.6、処理フロー 2.9</t>
-  </si>
-  <si>
-    <t>対象のグループ：CopySrc
-新しい名前：PkgCopy</t>
-  </si>
-  <si>
-    <t>コピーを押します。</t>
-  </si>
-  <si>
-    <t>一覧：PkgCopy が追加され、選ばれる
-ファイル：clients\PkgCopy.bat と clients\PkgCopy.xlsx が作られる
-画面の値：コピー元と同じ</t>
-  </si>
-  <si>
-    <t>画面設計 3.6、処理フロー 2.8</t>
-  </si>
-  <si>
-    <t>ファイル：clients\PkgCopy.bat と clients\PkgCopy.xlsx が作られる
-clients\CopySrc.bat の内容：generated\CopySrc を含む（変わらない）</t>
-  </si>
-  <si>
-    <t>ファイル：clients\PkgCopy.bat の内容：generated\PkgCopy を含む（パッケージの出力先の名前が新しいグループの名前になる）</t>
-  </si>
-  <si>
-    <t>対象のグループ：CopySrc
-サブドメイン：saved</t>
-  </si>
-  <si>
-    <t>設定ファイル（clients\CopySrc.bat）：saved を含む値が保存される
-ボタンの横の状態：完了</t>
-  </si>
-  <si>
-    <t>対象のグループ：CopySrc
-サブドメイン：tmp</t>
-  </si>
-  <si>
-    <t>サブドメイン：univ-kyousai-{x}（保存されている値）
-変えた内容：消える</t>
-  </si>
-  <si>
-    <t>画面設計 3.6、処理フロー 2.10</t>
-  </si>
-  <si>
-    <t>開く（対象のグループ）を押します。</t>
+    <t>ログの出力先：saved-log-path</t>
+  </si>
+  <si>
+    <t>「ログの出力先」を設定した後で、「保存」を押します。</t>
+  </si>
+  <si>
+    <t>設定ファイル（common.bat）：CommonLogPath=saved-log-path が保存される
+状態（保存）：完了</t>
+  </si>
+  <si>
+    <t>画面設計：3.5
+処理フロー：2.5</t>
+  </si>
+  <si>
+    <t>ログの出力先：tmp-reload</t>
+  </si>
+  <si>
+    <t>「ログの出力先」を設定した後で、「再読込」を押します。</t>
+  </si>
+  <si>
+    <t>ログの出力先：（保存されている値）
+状態（再読込）：完了</t>
+  </si>
+  <si>
+    <t>画面設計：3.5
+処理フロー：2.6</t>
+  </si>
+  <si>
+    <t>「再読込」を押します。</t>
+  </si>
+  <si>
+    <t>状態（再読込）：完了</t>
+  </si>
+  <si>
+    <t>対象のグループ：ok
+設定ファイル：ok.bat
+グループ名：TestNew</t>
+  </si>
+  <si>
+    <t>「新規作成」を押し、「グループ名」を入力して「OK」を押します。</t>
+  </si>
+  <si>
+    <t>一覧：TestNew が追加され、選ばれる</t>
+  </si>
+  <si>
+    <t>画面設計：3.6
+処理フロー：2.7</t>
+  </si>
+  <si>
+    <t>「新規作成」を押し、「グループ名」を入力して「OK」を押した後で、「保存」を押します。</t>
+  </si>
+  <si>
+    <t>状態（保存）：完了
+ファイル：TestNew.bat に KintoneSubdomain=univ-kyousai-{x} が保存される、TestNew.xlsx が作られる</t>
+  </si>
+  <si>
+    <t>画面設計：3.6
+処理フロー：2.7
+処理フロー：2.9</t>
+  </si>
+  <si>
+    <t>対象のグループ：ok
+設定ファイル：ok.bat
+Excel ファイル：ok.xlsx
+グループ名：TestCopy</t>
+  </si>
+  <si>
+    <t>「対象のグループ」を設定した後で、「コピー」を押し、「グループ名」を入力して「OK」を押します。</t>
+  </si>
+  <si>
+    <t>一覧：TestCopy が追加される
+ファイル：TestCopy.bat と TestCopy.xlsx が作られる</t>
+  </si>
+  <si>
+    <t>画面設計：3.6
+処理フロー：2.8</t>
+  </si>
+  <si>
+    <t>ok.bat の内容：generated\ok を含む
+ok.xlsx：残る</t>
+  </si>
+  <si>
+    <t>ファイル：TestCopy.bat の内容：TestCopy を含む（パッケージの出力先の名前が新しいグループの名前になる）</t>
+  </si>
+  <si>
+    <t>「対象のグループ」を設定した後で、「開く」を押します。</t>
   </si>
   <si>
     <t>開いた画面：対象のグループの Excel ファイル（ok.xlsx）</t>
   </si>
   <si>
-    <t>画面設計 3.6</t>
-  </si>
-  <si>
-    <t>対象のグループ：ok、入力なし（保存されている接続情報）</t>
-  </si>
-  <si>
-    <t>テスト接続（kintone接続）を押します。</t>
-  </si>
-  <si>
-    <t>ボタンの横の状態：成功</t>
-  </si>
-  <si>
-    <t>画面設計 3.6、処理フロー 2.11</t>
-  </si>
-  <si>
-    <t>対象のグループ：ok、入力なし（保存されている対象アプリID）</t>
-  </si>
-  <si>
-    <t>テスト接続（ファイル管理）を押します。</t>
-  </si>
-  <si>
-    <t>画面設計 3.6、処理フロー 2.12</t>
-  </si>
-  <si>
-    <t>対象のグループ：ok
-対象のシート：1,2</t>
-  </si>
-  <si>
-    <t>保存を押し、対象のグループを選び直します。</t>
-  </si>
-  <si>
-    <t>設定ファイル（clients\ok.bat）：GenerateSheetsInclude=1,2 が保存される
-対象のシート：1,2 が残る</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>新しい名前：ok（既存のグループ名）</t>
-  </si>
-  <si>
-    <t>メッセージ：「（入力した名前）は既に存在します。」
-一覧：追加されない</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>新規作成を押したあと、キャンセルを押します。</t>
-  </si>
-  <si>
-    <t>ファイル：clients\PkgCancel.bat が作られない
-一覧：変わらない</t>
+    <t>画面設計：3.6</t>
+  </si>
+  <si>
+    <t>対象のグループ：ok、入力なし（保存されている接続情報）
+設定ファイル：ok.bat</t>
+  </si>
+  <si>
+    <t>「対象のグループ」を設定した後で、「テスト接続（認証情報）」を押します。</t>
+  </si>
+  <si>
+    <t>状態（認証情報）：成功</t>
+  </si>
+  <si>
+    <t>画面設計：3.6
+処理フロー：2.11</t>
+  </si>
+  <si>
+    <t>対象のグループ：ok、入力なし（保存されている対象アプリID）
+設定ファイル：ok.bat</t>
+  </si>
+  <si>
+    <t>「対象のグループ」を設定した後で、「テスト接続（ファイル管理）」を押します。</t>
+  </si>
+  <si>
+    <t>状態（ファイル管理）：成功</t>
+  </si>
+  <si>
+    <t>画面設計：3.6
+処理フロー：2.12</t>
+  </si>
+  <si>
+    <t>「対象のグループ」を設定した後で、「再読込」を押します。</t>
+  </si>
+  <si>
+    <t>画面設計：3.6
+処理フロー：2.10</t>
+  </si>
+  <si>
+    <t>対象のグループ：ok
+サブドメイン：saved-subdomain
+設定ファイル：ok.bat
+Excel ファイル：ok.xlsx</t>
+  </si>
+  <si>
+    <t>「対象のグループ」と「サブドメイン」を設定した後で、「保存」を押します。</t>
+  </si>
+  <si>
+    <t>設定ファイル（ok.bat）：KintoneSubdomain=saved-subdomain が保存される
+状態（保存）：完了</t>
+  </si>
+  <si>
+    <t>画面設計：3.6
+処理フロー：2.9</t>
+  </si>
+  <si>
+    <t>対象のグループ：ok
+サブドメイン：tmp-reload
+設定ファイル：ok.bat
+Excel ファイル：ok.xlsx</t>
+  </si>
+  <si>
+    <t>「対象のグループ」と「サブドメイン」を設定した後で、「再読込」を押します。</t>
+  </si>
+  <si>
+    <t>サブドメイン：（保存されている値）
+変えた内容：消える
+状態（再読込）：完了</t>
+  </si>
+  <si>
+    <t>対象のグループ：ok
+ログイン名：テスト用の値
+設定ファイル：ok.bat</t>
+  </si>
+  <si>
+    <t>「対象のグループ」と「ログイン名」を設定した後で、「保存」を押します。</t>
+  </si>
+  <si>
+    <t>設定ファイル：ok.bat の KintoneLoginName が保存される
+状態（保存）：完了</t>
+  </si>
+  <si>
+    <t>対象のグループ：ok
+ログイン名：tmp-reload
+設定ファイル：ok.bat</t>
+  </si>
+  <si>
+    <t>「対象のグループ」と「ログイン名」を設定した後で、「再読込」を押します。</t>
+  </si>
+  <si>
+    <t>ログイン名：（保存されている値）
+変えた内容：消える
+状態（再読込）：完了</t>
   </si>
   <si>
     <t>14</t>
   </si>
   <si>
-    <t>新しい名前：PkgUnsaved</t>
-  </si>
-  <si>
-    <t>メッセージ：「コピー元のグループが存在しません」
-ファイル：clients\PkgUnsaved.bat が作られない</t>
+    <t>対象のグループ：ok
+パスワード：テスト用の値
+設定ファイル：ok.bat</t>
+  </si>
+  <si>
+    <t>「対象のグループ」と「パスワード」を設定した後で、「保存」を押します。</t>
+  </si>
+  <si>
+    <t>設定ファイル：ok.bat の KintonePassword が保存される
+状態（保存）：完了</t>
   </si>
   <si>
     <t>15</t>
   </si>
   <si>
-    <t>対象のグループ：CopySrc
-新しい名前：CopySrc</t>
-  </si>
-  <si>
-    <t>メッセージ：「（入力した名前）は既に存在します。」
-コピー：行われない</t>
+    <t>対象のグループ：ok
+対象アプリID：saved-app-id
+設定ファイル：ok.bat</t>
+  </si>
+  <si>
+    <t>「対象のグループ」と「対象アプリID」を設定した後で、「保存」を押します。</t>
+  </si>
+  <si>
+    <t>設定ファイル：ok.bat に saved-app-id が保存される
+状態（保存）：完了</t>
   </si>
   <si>
     <t>16</t>
   </si>
   <si>
     <t>対象のグループ：ok
-サブドメイン：空</t>
-  </si>
-  <si>
-    <t>ボタンの横の状態：失敗
-接続：行われない</t>
+対象アプリID：tmp-reload
+設定ファイル：ok.bat</t>
+  </si>
+  <si>
+    <t>「対象のグループ」と「対象アプリID」を設定した後で、「再読込」を押します。</t>
+  </si>
+  <si>
+    <t>対象アプリID：（保存されている値）
+変えた内容：消える
+状態（再読込）：完了</t>
   </si>
   <si>
     <t>17</t>
   </si>
   <si>
     <t>対象のグループ：ok
-パスワード：wrong-password</t>
-  </si>
-  <si>
-    <t>ボタンの横の状態：失敗</t>
+圧縮元のフォルダ：saved-source
+設定ファイル：ok.bat</t>
+  </si>
+  <si>
+    <t>「対象のグループ」と「圧縮元のフォルダ」を設定した後で、「保存」を押します。</t>
+  </si>
+  <si>
+    <t>設定ファイル：ok.bat に saved-source が保存される
+状態（保存）：完了</t>
   </si>
   <si>
     <t>18</t>
   </si>
   <si>
     <t>対象のグループ：ok
-対象アプリID：空</t>
+圧縮元のフォルダ：tmp-reload
+設定ファイル：ok.bat</t>
+  </si>
+  <si>
+    <t>「対象のグループ」と「圧縮元のフォルダ」を設定した後で、「再読込」を押します。</t>
+  </si>
+  <si>
+    <t>圧縮元のフォルダ：（保存されている値）
+変えた内容：消える
+状態（再読込）：完了</t>
   </si>
   <si>
     <t>19</t>
   </si>
   <si>
     <t>対象のグループ：ok
-対象アプリID：99999999</t>
+パッケージ定義ファイル：saved-config
+設定ファイル：ok.bat</t>
+  </si>
+  <si>
+    <t>「対象のグループ」と「パッケージ定義ファイル」を設定した後で、「保存」を押します。</t>
+  </si>
+  <si>
+    <t>設定ファイル：ok.bat に saved-config が保存される
+状態（保存）：完了</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>対象のグループ：ok
+パッケージ定義ファイル：tmp-reload
+設定ファイル：ok.bat</t>
+  </si>
+  <si>
+    <t>「対象のグループ」と「パッケージ定義ファイル」を設定した後で、「再読込」を押します。</t>
+  </si>
+  <si>
+    <t>パッケージ定義ファイル：（保存されている値）
+変えた内容：消える
+状態（再読込）：完了</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>対象のグループ：ok
+作業用のフォルダ：saved-work-folder
+設定ファイル：ok.bat</t>
+  </si>
+  <si>
+    <t>「対象のグループ」と「作業用のフォルダ」を設定した後で、「保存」を押します。</t>
+  </si>
+  <si>
+    <t>設定ファイル：ok.bat に saved-work-folder が保存される
+状態（保存）：完了</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>対象のグループ：ok
+作業用のフォルダ：tmp-reload
+設定ファイル：ok.bat</t>
+  </si>
+  <si>
+    <t>「対象のグループ」と「作業用のフォルダ」を設定した後で、「再読込」を押します。</t>
+  </si>
+  <si>
+    <t>作業用のフォルダ：（保存されている値）
+変えた内容：消える
+状態（再読込）：完了</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>対象のグループ：ok
+パッケージの出力先：saved-output
+設定ファイル：ok.bat</t>
+  </si>
+  <si>
+    <t>「対象のグループ」と「パッケージの出力先」を設定した後で、「保存」を押します。</t>
+  </si>
+  <si>
+    <t>設定ファイル：ok.bat に saved-output が保存される
+状態（保存）：完了</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>対象のグループ：ok
+パッケージの出力先：tmp-reload
+設定ファイル：ok.bat</t>
+  </si>
+  <si>
+    <t>「対象のグループ」と「パッケージの出力先」を設定した後で、「再読込」を押します。</t>
+  </si>
+  <si>
+    <t>パッケージの出力先：（保存されている値）
+変えた内容：消える
+状態（再読込）：完了</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>対象のグループ：ok、ng、ok
+対象のシート：saved-sheets
+設定ファイル：ok.bat</t>
+  </si>
+  <si>
+    <t>「対象のグループ」と「対象のシート」を設定した後で、「保存」を押した後で、「対象のグループ」を設定し直します。</t>
+  </si>
+  <si>
+    <t>設定ファイル（ok.bat）：GenerateSheetsInclude=saved-sheets が保存される
+状態（保存）：完了
+対象のシート：saved-sheets が残る</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>対象のグループ：ok
+対象のシート：tmp-reload
+設定ファイル：ok.bat</t>
+  </si>
+  <si>
+    <t>「対象のグループ」と「対象のシート」を設定した後で、「再読込」を押します。</t>
+  </si>
+  <si>
+    <t>対象のシート：空（保存されている値）
+変えた内容：消える
+状態（再読込）：完了</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>対象のグループ：ok
+除外のシート：saved-exclude-sheets
+設定ファイル：ok.bat</t>
+  </si>
+  <si>
+    <t>「対象のグループ」と「除外のシート」を設定した後で、「保存」を押します。</t>
+  </si>
+  <si>
+    <t>設定ファイル：ok.bat に GenerateSheetsExclude=saved-exclude-sheets が保存される
+状態（保存）：完了</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>対象のグループ：ok
+除外のシート：tmp-reload
+設定ファイル：ok.bat</t>
+  </si>
+  <si>
+    <t>「対象のグループ」と「除外のシート」を設定した後で、「再読込」を押します。</t>
+  </si>
+  <si>
+    <t>除外のシート：空（保存されている値）
+変えた内容：消える
+状態（再読込）：完了</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>対象のグループ：ok
+設定ファイル：ok.bat
+グループ名：ok（既存のグループ名）</t>
+  </si>
+  <si>
+    <t>メッセージ：「（入力した名前）は既に存在します。」</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>「対象のグループ」を設定した後で、「新規作成」を押した後で、「キャンセル」を押します。</t>
+  </si>
+  <si>
+    <t>ファイル：TestCancel.bat が作られない</t>
+  </si>
+  <si>
+    <t>31</t>
+  </si>
+  <si>
+    <t>対象のグループ：ok
+設定ファイル：ok.bat
+グループ名：TestUnsaved</t>
+  </si>
+  <si>
+    <t>「新規作成」を押し、「グループ名」を入力して「OK」を押した後で、「コピー」を押します。</t>
+  </si>
+  <si>
+    <t>メッセージ：「コピー元のグループが存在しません。」
+ファイル：TestUnsaved.bat が作られない</t>
+  </si>
+  <si>
+    <t>32</t>
+  </si>
+  <si>
+    <t>対象のグループ：ok
+設定ファイル：ok.bat
+Excel ファイル：ok.xlsx
+グループ名：ok（既存のグループ名）</t>
+  </si>
+  <si>
+    <t>33</t>
+  </si>
+  <si>
+    <t>対象のグループ：ok
+サブドメイン：空
+設定ファイル：ok.bat</t>
+  </si>
+  <si>
+    <t>メッセージ：「エラーが発生しました: サブドメイン・ログイン名・パスワードをすべて入力してください。」
+状態（認証情報）：失敗</t>
+  </si>
+  <si>
+    <t>34</t>
+  </si>
+  <si>
+    <t>対象のグループ：ok
+パスワード：誤った値
+設定ファイル：ok.bat</t>
+  </si>
+  <si>
+    <t>「対象のグループ」と「パスワード」を設定した後で、「テスト接続（認証情報）」を押します。</t>
+  </si>
+  <si>
+    <t>状態（認証情報）：失敗</t>
+  </si>
+  <si>
+    <t>35</t>
   </si>
   <si>
     <t>対象のグループ：ng
-パスワード：wrong-password</t>
+パスワード：誤った値
+設定ファイル：ng.bat</t>
+  </si>
+  <si>
+    <t>36</t>
+  </si>
+  <si>
+    <t>対象のグループ：ok
+対象アプリID：空
+設定ファイル：ok.bat</t>
+  </si>
+  <si>
+    <t>状態（ファイル管理）：失敗</t>
+  </si>
+  <si>
+    <t>対象のグループ：ok
+対象アプリID：99999999
+設定ファイル：ok.bat</t>
+  </si>
+  <si>
+    <t>「対象のグループ」と「対象アプリID」を設定した後で、「テスト接続（ファイル管理）」を押します。</t>
+  </si>
+  <si>
+    <t>状態：成功</t>
+  </si>
+  <si>
+    <t>画面設計：3.7
+処理フロー：2.13</t>
   </si>
   <si>
     <t>状態：成功
-テンプレートシートの 2 行目以降：圧縮元のフォルダの内容で作り直される
-ログ：表示される</t>
-  </si>
-  <si>
-    <t>画面設計 3.7、処理フロー 2.13</t>
-  </si>
-  <si>
-    <t>対象のグループ：ok
-テンプレート（A2）：MARKER_ROW2（準備で書き込み）</t>
-  </si>
-  <si>
-    <t>状態：成功
-テンプレートシートの 2 行目：消去される</t>
-  </si>
-  <si>
-    <t>画面設計 3.7、処理フロー 2.13、処理フロー 3</t>
+テンプレートシートの A2：書き換えられる（MARKER_ROW2 のままではなく、空でもない）</t>
   </si>
   <si>
     <t>開いた画面：更新されたパッケージ定義ファイル（ok.xlsx）</t>
   </si>
   <si>
-    <t>画面設計 3.7</t>
-  </si>
-  <si>
-    <t>対象のグループ：ok
-パッケージ定義ファイル：Excel で開いたまま</t>
+    <t>画面設計：3.7</t>
+  </si>
+  <si>
+    <t>対象のグループ：ok
+パッケージ定義ファイル：Excel で開いたまま
+設定ファイル：ok.bat</t>
   </si>
 </sst>
 </file>
@@ -1033,13 +1400,12 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8FF4B9FB-990D-459A-9A77-EEDE0EB88ABD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{15029C17-5074-40A2-89DE-F44042D6BBE9}">
   <dimension ref="A1:C8"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="8.69921875" customWidth="1"/>
-    <col min="2" max="2" width="18.69921875" customWidth="1"/>
-    <col min="3" max="3" width="10.69921875" customWidth="1"/>
+    <col min="2" max="3" width="18.69921875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.45">
@@ -1094,18 +1460,18 @@
         <v>13</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="36" x14ac:dyDescent="0.45">
       <c r="A6" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="54" x14ac:dyDescent="0.45">
@@ -1113,15 +1479,15 @@
         <v>8</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="72" x14ac:dyDescent="0.45">
       <c r="A8" s="2" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>19</v>
@@ -1131,23 +1497,21 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C8" xr:uid="{8FF4B9FB-990D-459A-9A77-EEDE0EB88ABD}"/>
+  <autoFilter ref="A1:C8" xr:uid="{15029C17-5074-40A2-89DE-F44042D6BBE9}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6FFF4174-91F5-4E15-B1D0-FEB7DB5692D3}">
-  <dimension ref="A1:G10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9791B7D3-430C-4205-B52F-60FDDB209F8E}">
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="8.69921875" customWidth="1"/>
     <col min="2" max="2" width="10.69921875" customWidth="1"/>
-    <col min="3" max="3" width="50.69921875" customWidth="1"/>
-    <col min="4" max="4" width="45.69921875" customWidth="1"/>
-    <col min="5" max="5" width="75.69921875" customWidth="1"/>
-    <col min="6" max="6" width="28.69921875" customWidth="1"/>
+    <col min="3" max="5" width="70.69921875" customWidth="1"/>
+    <col min="6" max="6" width="20.69921875" customWidth="1"/>
     <col min="7" max="7" width="12.69921875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1174,7 +1538,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="180" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:7" ht="288" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
@@ -1197,7 +1561,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="180" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:7" ht="270" x14ac:dyDescent="0.45">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
@@ -1208,10 +1572,10 @@
         <v>32</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>30</v>
@@ -1220,15 +1584,15 @@
         <v>31</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="162" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:7" ht="324" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>26</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>35</v>
@@ -1243,15 +1607,15 @@
         <v>31</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="108" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:7" ht="270" x14ac:dyDescent="0.45">
       <c r="A5" s="2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>26</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>37</v>
@@ -1266,21 +1630,21 @@
         <v>31</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="108" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:7" ht="306" x14ac:dyDescent="0.45">
       <c r="A6" s="2" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>30</v>
@@ -1289,18 +1653,18 @@
         <v>31</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="162" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:7" ht="324" x14ac:dyDescent="0.45">
       <c r="A7" s="2" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>42</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>43</v>
@@ -1312,21 +1676,21 @@
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="162" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:7" ht="288" x14ac:dyDescent="0.45">
       <c r="A8" s="2" t="s">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>30</v>
@@ -1335,21 +1699,21 @@
         <v>31</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="270" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:7" ht="360" x14ac:dyDescent="0.45">
       <c r="A9" s="2" t="s">
-        <v>46</v>
+        <v>5</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>47</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>30</v>
@@ -1358,47 +1722,22 @@
         <v>31</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="180" x14ac:dyDescent="0.45">
-      <c r="A10" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:G10" xr:uid="{6FFF4174-91F5-4E15-B1D0-FEB7DB5692D3}"/>
+  <autoFilter ref="A1:G9" xr:uid="{9791B7D3-430C-4205-B52F-60FDDB209F8E}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D5AA3FF-5737-448C-87CB-6953374C3070}">
-  <dimension ref="A1:G7"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC1C3C90-61DA-4FB9-8596-D08A0E4C636E}">
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="8.69921875" customWidth="1"/>
     <col min="2" max="2" width="10.69921875" customWidth="1"/>
-    <col min="3" max="3" width="50.69921875" customWidth="1"/>
-    <col min="4" max="4" width="45.69921875" customWidth="1"/>
-    <col min="5" max="5" width="75.69921875" customWidth="1"/>
-    <col min="6" max="6" width="28.69921875" customWidth="1"/>
+    <col min="3" max="5" width="70.69921875" customWidth="1"/>
+    <col min="6" max="6" width="20.69921875" customWidth="1"/>
     <col min="7" max="7" width="12.69921875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1425,7 +1764,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="270" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:7" ht="198" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
@@ -1433,7 +1772,7 @@
         <v>26</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>28</v>
@@ -1448,7 +1787,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="90" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:7" ht="180" x14ac:dyDescent="0.45">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
@@ -1456,13 +1795,13 @@
         <v>26</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>52</v>
@@ -1471,21 +1810,21 @@
         <v>31</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="108" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:7" ht="126" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>26</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>34</v>
+        <v>56</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>52</v>
@@ -1494,21 +1833,21 @@
         <v>31</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="72" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:7" ht="162" x14ac:dyDescent="0.45">
       <c r="A5" s="2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>28</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>52</v>
@@ -1517,12 +1856,12 @@
         <v>31</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="90" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:7" ht="216" x14ac:dyDescent="0.45">
       <c r="A6" s="2" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>59</v>
@@ -1540,47 +1879,22 @@
         <v>31</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="180" x14ac:dyDescent="0.45">
-      <c r="A7" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:G7" xr:uid="{8D5AA3FF-5737-448C-87CB-6953374C3070}"/>
+  <autoFilter ref="A1:G6" xr:uid="{DC1C3C90-61DA-4FB9-8596-D08A0E4C636E}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3FEFF57A-18BB-41CB-9A64-BE88581CD6BE}">
-  <dimension ref="A1:G12"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B78F4675-43FC-4860-9EAC-039548FB589D}">
+  <dimension ref="A1:G14"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="8.69921875" customWidth="1"/>
     <col min="2" max="2" width="10.69921875" customWidth="1"/>
-    <col min="3" max="3" width="50.69921875" customWidth="1"/>
-    <col min="4" max="4" width="45.69921875" customWidth="1"/>
-    <col min="5" max="5" width="75.69921875" customWidth="1"/>
-    <col min="6" max="6" width="28.69921875" customWidth="1"/>
+    <col min="3" max="5" width="70.69921875" customWidth="1"/>
+    <col min="6" max="6" width="20.69921875" customWidth="1"/>
     <col min="7" max="7" width="12.69921875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1607,7 +1921,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="198" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:7" ht="409.6" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
@@ -1615,22 +1929,22 @@
         <v>26</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="F2" s="2" t="s">
-        <v>65</v>
-      </c>
       <c r="G2" s="2" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="216" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:7" ht="324" x14ac:dyDescent="0.45">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
@@ -1638,22 +1952,22 @@
         <v>26</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>28</v>
-      </c>
       <c r="E3" s="2" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="198" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:7" ht="409.6" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
         <v>9</v>
       </c>
@@ -1661,22 +1975,22 @@
         <v>26</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>28</v>
+        <v>67</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>68</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="234" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:7" ht="409.6" x14ac:dyDescent="0.45">
       <c r="A5" s="2" t="s">
         <v>12</v>
       </c>
@@ -1687,27 +2001,27 @@
         <v>69</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>28</v>
+        <v>70</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="126" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:7" ht="324" x14ac:dyDescent="0.45">
       <c r="A6" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>26</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>72</v>
@@ -1722,7 +2036,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="144" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:7" ht="378" x14ac:dyDescent="0.45">
       <c r="A7" s="2" t="s">
         <v>8</v>
       </c>
@@ -1745,21 +2059,21 @@
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="90" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:7" ht="378" x14ac:dyDescent="0.45">
       <c r="A8" s="2" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>26</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>34</v>
+        <v>78</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>53</v>
+        <v>79</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>74</v>
@@ -1768,116 +2082,160 @@
         <v>31</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="162" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:7" ht="378" x14ac:dyDescent="0.45">
       <c r="A9" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>28</v>
+        <v>82</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="180" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:7" ht="198" x14ac:dyDescent="0.45">
       <c r="A10" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>80</v>
+        <v>53</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>28</v>
+        <v>84</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="198" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:7" ht="144" x14ac:dyDescent="0.45">
       <c r="A11" s="2" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>63</v>
+        <v>87</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>28</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="198" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:7" ht="306" x14ac:dyDescent="0.45">
       <c r="A12" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="396" x14ac:dyDescent="0.45">
+      <c r="A13" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="378" x14ac:dyDescent="0.45">
+      <c r="A14" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="G12" s="2" t="s">
+      <c r="B14" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="G14" s="2" t="s">
         <v>31</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G12" xr:uid="{3FEFF57A-18BB-41CB-9A64-BE88581CD6BE}"/>
+  <autoFilter ref="A1:G14" xr:uid="{B78F4675-43FC-4860-9EAC-039548FB589D}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1301CEB6-1811-492F-93C6-7F26D4B04289}">
-  <dimension ref="A1:G7"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08E2BB7B-6CB3-425F-B888-8A10BB987266}">
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="8.69921875" customWidth="1"/>
     <col min="2" max="2" width="10.69921875" customWidth="1"/>
-    <col min="3" max="3" width="50.69921875" customWidth="1"/>
-    <col min="4" max="4" width="45.69921875" customWidth="1"/>
-    <col min="5" max="5" width="75.69921875" customWidth="1"/>
-    <col min="6" max="6" width="28.69921875" customWidth="1"/>
+    <col min="3" max="5" width="70.69921875" customWidth="1"/>
+    <col min="6" max="6" width="20.69921875" customWidth="1"/>
     <col min="7" max="7" width="12.69921875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1904,7 +2262,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="126" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:7" ht="270" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
@@ -1912,22 +2270,22 @@
         <v>26</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>31</v>
+        <v>98</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="126" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:7" ht="252" x14ac:dyDescent="0.45">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
@@ -1935,22 +2293,22 @@
         <v>26</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="126" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:7" ht="198" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
         <v>9</v>
       </c>
@@ -1958,22 +2316,22 @@
         <v>26</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>91</v>
+        <v>106</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>94</v>
+        <v>107</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>89</v>
+        <v>108</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="270" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:7" ht="396" x14ac:dyDescent="0.45">
       <c r="A5" s="2" t="s">
         <v>12</v>
       </c>
@@ -1981,85 +2339,60 @@
         <v>26</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="90" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:7" ht="216" x14ac:dyDescent="0.45">
       <c r="A6" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="126" x14ac:dyDescent="0.45">
-      <c r="A7" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:G7" xr:uid="{1301CEB6-1811-492F-93C6-7F26D4B04289}"/>
+  <autoFilter ref="A1:G6" xr:uid="{08E2BB7B-6CB3-425F-B888-8A10BB987266}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{821A0272-3AC1-49F3-A1C0-39770D1CE2CE}">
-  <dimension ref="A1:G3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{373A4BCC-C738-48E7-8CF4-A1495BD6FD1A}">
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="8.69921875" customWidth="1"/>
     <col min="2" max="2" width="10.69921875" customWidth="1"/>
-    <col min="3" max="3" width="50.69921875" customWidth="1"/>
-    <col min="4" max="4" width="45.69921875" customWidth="1"/>
-    <col min="5" max="5" width="75.69921875" customWidth="1"/>
-    <col min="6" max="6" width="28.69921875" customWidth="1"/>
+    <col min="3" max="5" width="70.69921875" customWidth="1"/>
+    <col min="6" max="6" width="20.69921875" customWidth="1"/>
     <col min="7" max="7" width="12.69921875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2086,7 +2419,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="288" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:7" ht="234" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
@@ -2094,22 +2427,22 @@
         <v>26</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>105</v>
+        <v>116</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="198" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:7" ht="144" x14ac:dyDescent="0.45">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
@@ -2117,39 +2450,60 @@
         <v>26</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>109</v>
+        <v>120</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>31</v>
       </c>
     </row>
+    <row r="4" spans="1:7" ht="72" x14ac:dyDescent="0.45">
+      <c r="A4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G3" xr:uid="{821A0272-3AC1-49F3-A1C0-39770D1CE2CE}"/>
+  <autoFilter ref="A1:G4" xr:uid="{373A4BCC-C738-48E7-8CF4-A1495BD6FD1A}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30FDBC43-3B6B-4C99-9B50-6CF255973405}">
-  <dimension ref="A1:G21"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCDC749E-B680-416E-A337-277EF4F56C1D}">
+  <dimension ref="A1:G38"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="8.69921875" customWidth="1"/>
     <col min="2" max="2" width="10.69921875" customWidth="1"/>
-    <col min="3" max="3" width="50.69921875" customWidth="1"/>
-    <col min="4" max="4" width="45.69921875" customWidth="1"/>
-    <col min="5" max="5" width="75.69921875" customWidth="1"/>
-    <col min="6" max="6" width="28.69921875" customWidth="1"/>
+    <col min="3" max="5" width="70.69921875" customWidth="1"/>
+    <col min="6" max="6" width="20.69921875" customWidth="1"/>
     <col min="7" max="7" width="12.69921875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2176,7 +2530,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="90" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:7" ht="162" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
@@ -2184,22 +2538,22 @@
         <v>26</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>111</v>
+        <v>124</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>112</v>
+        <v>125</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>113</v>
+        <v>126</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="216" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:7" ht="306" x14ac:dyDescent="0.45">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
@@ -2207,22 +2561,22 @@
         <v>26</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>111</v>
+        <v>124</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>104</v>
+        <v>128</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="324" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:7" ht="234" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
         <v>9</v>
       </c>
@@ -2230,22 +2584,22 @@
         <v>26</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>117</v>
+        <v>131</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>118</v>
+        <v>132</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>119</v>
+        <v>133</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>120</v>
+        <v>134</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="324" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:7" ht="234" x14ac:dyDescent="0.45">
       <c r="A5" s="2" t="s">
         <v>12</v>
       </c>
@@ -2253,45 +2607,45 @@
         <v>26</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>117</v>
+        <v>131</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>118</v>
+        <v>132</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>121</v>
+        <v>135</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>120</v>
+        <v>134</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="306" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:7" ht="270" x14ac:dyDescent="0.45">
       <c r="A6" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>26</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>117</v>
+        <v>131</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>118</v>
+        <v>132</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>122</v>
+        <v>136</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>120</v>
+        <v>134</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="216" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:7" ht="144" x14ac:dyDescent="0.45">
       <c r="A7" s="2" t="s">
         <v>8</v>
       </c>
@@ -2299,16 +2653,16 @@
         <v>26</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>123</v>
+        <v>53</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>104</v>
+        <v>137</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>124</v>
+        <v>138</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>116</v>
+        <v>139</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>31</v>
@@ -2316,51 +2670,51 @@
     </row>
     <row r="8" spans="1:7" ht="180" x14ac:dyDescent="0.45">
       <c r="A8" s="2" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>26</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>125</v>
+        <v>140</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>108</v>
+        <v>141</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>126</v>
+        <v>142</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>127</v>
+        <v>143</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="144" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:7" ht="198" x14ac:dyDescent="0.45">
       <c r="A9" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>26</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>34</v>
+        <v>144</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>128</v>
+        <v>145</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>129</v>
+        <v>146</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>130</v>
+        <v>147</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="126" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:7" ht="144" x14ac:dyDescent="0.45">
       <c r="A10" s="2" t="s">
         <v>5</v>
       </c>
@@ -2368,39 +2722,39 @@
         <v>26</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>131</v>
+        <v>53</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>132</v>
+        <v>148</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>134</v>
+        <v>149</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="144" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:7" ht="270" x14ac:dyDescent="0.45">
       <c r="A11" s="2" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>26</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>135</v>
+        <v>150</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>136</v>
+        <v>151</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>133</v>
+        <v>152</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>137</v>
+        <v>153</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>31</v>
@@ -2408,22 +2762,22 @@
     </row>
     <row r="12" spans="1:7" ht="252" x14ac:dyDescent="0.45">
       <c r="A12" s="2" t="s">
-        <v>11</v>
+        <v>89</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>26</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>138</v>
+        <v>154</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>116</v>
+        <v>149</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>31</v>
@@ -2431,68 +2785,68 @@
     </row>
     <row r="13" spans="1:7" ht="180" x14ac:dyDescent="0.45">
       <c r="A13" s="2" t="s">
-        <v>141</v>
+        <v>93</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>142</v>
+        <v>157</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>112</v>
+        <v>158</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="144" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:7" ht="180" x14ac:dyDescent="0.45">
       <c r="A14" s="2" t="s">
-        <v>144</v>
+        <v>11</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>31</v>
+        <v>160</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>145</v>
+        <v>161</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>146</v>
+        <v>162</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>114</v>
+        <v>149</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="234" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:7" ht="180" x14ac:dyDescent="0.45">
       <c r="A15" s="2" t="s">
-        <v>147</v>
+        <v>163</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>148</v>
+        <v>164</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>118</v>
+        <v>165</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>149</v>
+        <v>166</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>31</v>
@@ -2500,160 +2854,549 @@
     </row>
     <row r="16" spans="1:7" ht="180" x14ac:dyDescent="0.45">
       <c r="A16" s="2" t="s">
-        <v>150</v>
+        <v>167</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>151</v>
+        <v>168</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>118</v>
+        <v>169</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>152</v>
+        <v>170</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="108" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:7" ht="198" x14ac:dyDescent="0.45">
       <c r="A17" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="198" x14ac:dyDescent="0.45">
+      <c r="A18" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="198" x14ac:dyDescent="0.45">
+      <c r="A19" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="216" x14ac:dyDescent="0.45">
+      <c r="A20" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="216" x14ac:dyDescent="0.45">
+      <c r="A21" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="216" x14ac:dyDescent="0.45">
+      <c r="A22" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="F22" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="B17" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="D17" s="2" t="s">
+      <c r="G22" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="198" x14ac:dyDescent="0.45">
+      <c r="A23" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="198" x14ac:dyDescent="0.45">
+      <c r="A24" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="198" x14ac:dyDescent="0.45">
+      <c r="A25" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="342" x14ac:dyDescent="0.45">
+      <c r="A26" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="198" x14ac:dyDescent="0.45">
+      <c r="A27" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="252" x14ac:dyDescent="0.45">
+      <c r="A28" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="198" x14ac:dyDescent="0.45">
+      <c r="A29" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="198" x14ac:dyDescent="0.45">
+      <c r="A30" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="216" x14ac:dyDescent="0.45">
+      <c r="A31" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="234" x14ac:dyDescent="0.45">
+      <c r="A32" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="270" x14ac:dyDescent="0.45">
+      <c r="A33" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="D33" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="E17" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="F17" s="2" t="s">
+      <c r="E33" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="F33" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="G17" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" ht="126" x14ac:dyDescent="0.45">
-      <c r="A18" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" ht="90" x14ac:dyDescent="0.45">
-      <c r="A19" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" ht="108" x14ac:dyDescent="0.45">
-      <c r="A20" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" ht="126" x14ac:dyDescent="0.45">
-      <c r="A21" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="G21" s="2" t="s">
+      <c r="G33" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="306" x14ac:dyDescent="0.45">
+      <c r="A34" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="G34" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="234" x14ac:dyDescent="0.45">
+      <c r="A35" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="G35" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="234" x14ac:dyDescent="0.45">
+      <c r="A36" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="G36" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" ht="198" x14ac:dyDescent="0.45">
+      <c r="A37" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="G37" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="252" x14ac:dyDescent="0.45">
+      <c r="A38" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="G38" s="2" t="s">
         <v>31</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G21" xr:uid="{30FDBC43-3B6B-4C99-9B50-6CF255973405}"/>
+  <autoFilter ref="A1:G38" xr:uid="{DCDC749E-B680-416E-A337-277EF4F56C1D}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE88AF5E-B95B-45EB-B4E1-F6A99777299A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF7D0ABF-F9AF-49BD-9DD2-11F2377E8538}">
   <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="8.69921875" customWidth="1"/>
     <col min="2" max="2" width="10.69921875" customWidth="1"/>
-    <col min="3" max="3" width="50.69921875" customWidth="1"/>
-    <col min="4" max="4" width="45.69921875" customWidth="1"/>
-    <col min="5" max="5" width="75.69921875" customWidth="1"/>
-    <col min="6" max="6" width="28.69921875" customWidth="1"/>
+    <col min="3" max="5" width="70.69921875" customWidth="1"/>
+    <col min="6" max="6" width="20.69921875" customWidth="1"/>
     <col min="7" max="7" width="12.69921875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2680,7 +3423,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="234" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:7" ht="198" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
@@ -2688,22 +3431,22 @@
         <v>26</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>28</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>164</v>
+        <v>249</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>165</v>
+        <v>250</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="198" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:7" ht="252" x14ac:dyDescent="0.45">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
@@ -2711,22 +3454,22 @@
         <v>26</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>166</v>
+        <v>53</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>28</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>167</v>
+        <v>251</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>168</v>
+        <v>250</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="144" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:7" ht="180" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
         <v>9</v>
       </c>
@@ -2734,46 +3477,46 @@
         <v>26</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>169</v>
+        <v>252</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>170</v>
+        <v>253</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="162" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:7" ht="216" x14ac:dyDescent="0.45">
       <c r="A5" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>171</v>
+        <v>254</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>28</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>168</v>
+        <v>250</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>31</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G5" xr:uid="{AE88AF5E-B95B-45EB-B4E1-F6A99777299A}"/>
+  <autoFilter ref="A1:G5" xr:uid="{FF7D0ABF-F9AF-49BD-9DD2-11F2377E8538}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/tool/package-generator/doc/03_結合テスト/テスト仕様書.xlsx
+++ b/tool/package-generator/doc/03_結合テスト/テスト仕様書.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\myrepo\project_management\tool\package-generator\doc\03_結合テスト\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4DAD7A06-F234-4060-A1A0-A6BC85E8DDEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6772E09E-FADE-4BAA-9459-181865FF2071}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{4971C1B8-85C2-4425-8B28-13C5BBA0ED00}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{2326F0BB-6FE5-4BBE-811B-37C5A426EA4C}"/>
   </bookViews>
   <sheets>
     <sheet name="一覧" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="598" uniqueCount="255">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="598" uniqueCount="254">
   <si>
     <t>通番</t>
   </si>
@@ -59,7 +59,7 @@
     <t>実行（一括実行）</t>
   </si>
   <si>
-    <t>9</t>
+    <t>8</t>
   </si>
   <si>
     <t>2</t>
@@ -68,37 +68,37 @@
     <t>実行（パッケージ作成）</t>
   </si>
   <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>実行（パッケージ反映）</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>ログ</t>
+  </si>
+  <si>
+    <t>環境設定（共通）</t>
+  </si>
+  <si>
     <t>6</t>
   </si>
   <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>実行（パッケージ反映）</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>ログ</t>
+    <t>環境設定（グループ別）</t>
+  </si>
+  <si>
+    <t>37</t>
   </si>
   <si>
     <t>7</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>環境設定（共通）</t>
-  </si>
-  <si>
-    <t>環境設定（グループ別）</t>
-  </si>
-  <si>
-    <t>37</t>
   </si>
   <si>
     <t>環境設定（パッケージ定義）</t>
@@ -155,7 +155,7 @@
     <t>「対象のグループ」を設定した後で、「パッケージのアップロード」にチェックを入れて、「実行」を押します。</t>
   </si>
   <si>
-    <t>状態（パッケージの作成）：成功
+    <t>状態（パッケージの作成）：成功または警告
 状態（パッケージのアップロード）：成功
 状態：成功または警告</t>
   </si>
@@ -163,7 +163,7 @@
     <t>「対象のグループ」を設定した後で、「実行」を押した後で、「開く（パッケージの作成）」を押します。</t>
   </si>
   <si>
-    <t>開く（パッケージの作成）：作成したパッケージの出力先のフォルダ
+    <t>開く（パッケージの作成）：出力先のフォルダ
 状態（パッケージの作成）：成功または警告
 状態：成功または警告</t>
   </si>
@@ -171,7 +171,7 @@
     <t>「対象のグループ」を設定した後で、「実行」を押した後で、「開く（パッケージのアップロード）」を押します。</t>
   </si>
   <si>
-    <t>開いた画面：ファイル管理</t>
+    <t>開く：テスト用のアプリ（ファイル管理）</t>
   </si>
   <si>
     <t>異常系</t>
@@ -199,9 +199,6 @@
     <t>メッセージ：「フォルダ を設定してください。」</t>
   </si>
   <si>
-    <t>8</t>
-  </si>
-  <si>
     <t>対象のグループ：ng（圧縮元のフォルダがない）
 パッケージの作成：あり
 パッケージのアップロード：あり
@@ -213,6 +210,9 @@
 状態：失敗</t>
   </si>
   <si>
+    <t>9</t>
+  </si>
+  <si>
     <t>対象のグループ：ng
 パッケージの作成：なし
 パッケージのアップロード：あり
@@ -232,7 +232,7 @@
   </si>
   <si>
     <t>状態：成功
-パッケージの出力先（ok）：作られる</t>
+パッケージ：作られる</t>
   </si>
   <si>
     <t>画面設計：3.2
@@ -246,7 +246,7 @@
     <t>「対象のグループ」を設定した後で、「実行」を押した後で、「開く」を押します。</t>
   </si>
   <si>
-    <t>開いた画面：パッケージの出力先のフォルダ</t>
+    <t>開く：出力先のフォルダ</t>
   </si>
   <si>
     <t>対象のグループ：warn</t>
@@ -358,9 +358,6 @@
   </si>
   <si>
     <t>「実行（パッケージ反映）」で「対象のグループ」を設定した後で、「開く」を押します。</t>
-  </si>
-  <si>
-    <t>開いた画面：ファイル管理（未確認）</t>
   </si>
   <si>
     <t>10</t>
@@ -520,7 +517,7 @@
   </si>
   <si>
     <t>状態（保存）：完了
-ファイル：TestNew.bat に KintoneSubdomain=univ-kyousai-{x} が保存される、TestNew.xlsx が作られる</t>
+ファイル：TestNew.bat に KintoneSubdomain=univ-kyousai-{x} が保存される、TestNew.xlsx</t>
   </si>
   <si>
     <t>画面設計：3.6
@@ -538,7 +535,7 @@
   </si>
   <si>
     <t>一覧：TestCopy が追加される
-ファイル：TestCopy.bat と TestCopy.xlsx が作られる</t>
+ファイル：TestCopy.bat と TestCopy.xlsx</t>
   </si>
   <si>
     <t>画面設計：3.6
@@ -555,7 +552,7 @@
     <t>「対象のグループ」を設定した後で、「開く」を押します。</t>
   </si>
   <si>
-    <t>開いた画面：対象のグループの Excel ファイル（ok.xlsx）</t>
+    <t>開く：対象のグループの Excel ファイル（ok.xlsx）</t>
   </si>
   <si>
     <t>画面設計：3.6</t>
@@ -993,7 +990,7 @@
 テンプレートシートの A2：書き換えられる（MARKER_ROW2 のままではなく、空でもない）</t>
   </si>
   <si>
-    <t>開いた画面：更新されたパッケージ定義ファイル（ok.xlsx）</t>
+    <t>開く：更新されたパッケージ定義ファイル（ok.xlsx）</t>
   </si>
   <si>
     <t>画面設計：3.7</t>
@@ -1400,7 +1397,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{15029C17-5074-40A2-89DE-F44042D6BBE9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB06E082-9175-4E30-A834-E0E870E3199E}">
   <dimension ref="A1:C8"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -1460,15 +1457,15 @@
         <v>13</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="36" x14ac:dyDescent="0.45">
       <c r="A6" s="2" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>9</v>
@@ -1476,18 +1473,18 @@
     </row>
     <row r="7" spans="1:3" ht="54" x14ac:dyDescent="0.45">
       <c r="A7" s="2" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="B7" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="72" x14ac:dyDescent="0.45">
       <c r="A8" s="2" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>19</v>
@@ -1497,14 +1494,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C8" xr:uid="{15029C17-5074-40A2-89DE-F44042D6BBE9}"/>
+  <autoFilter ref="A1:C8" xr:uid="{EB06E082-9175-4E30-A834-E0E870E3199E}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9791B7D3-430C-4205-B52F-60FDDB209F8E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7DCBCEF-0881-4966-9558-FA97634E44A6}">
   <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -1561,7 +1558,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="270" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:7" ht="288" x14ac:dyDescent="0.45">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
@@ -1584,7 +1581,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="324" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:7" ht="270" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
         <v>12</v>
       </c>
@@ -1609,7 +1606,7 @@
     </row>
     <row r="5" spans="1:7" ht="270" x14ac:dyDescent="0.45">
       <c r="A5" s="2" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>26</v>
@@ -1632,7 +1629,7 @@
     </row>
     <row r="6" spans="1:7" ht="306" x14ac:dyDescent="0.45">
       <c r="A6" s="2" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>39</v>
@@ -1655,7 +1652,7 @@
     </row>
     <row r="7" spans="1:7" ht="324" x14ac:dyDescent="0.45">
       <c r="A7" s="2" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>39</v>
@@ -1678,19 +1675,19 @@
     </row>
     <row r="8" spans="1:7" ht="288" x14ac:dyDescent="0.45">
       <c r="A8" s="2" t="s">
-        <v>44</v>
+        <v>5</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>39</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>30</v>
@@ -1701,7 +1698,7 @@
     </row>
     <row r="9" spans="1:7" ht="360" x14ac:dyDescent="0.45">
       <c r="A9" s="2" t="s">
-        <v>5</v>
+        <v>46</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>39</v>
@@ -1723,14 +1720,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G9" xr:uid="{9791B7D3-430C-4205-B52F-60FDDB209F8E}"/>
+  <autoFilter ref="A1:G9" xr:uid="{A7DCBCEF-0881-4966-9558-FA97634E44A6}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC1C3C90-61DA-4FB9-8596-D08A0E4C636E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70B4234C-EC6B-4C15-BA3A-33D9AF79CB16}">
   <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -1835,7 +1832,7 @@
     </row>
     <row r="5" spans="1:7" ht="162" x14ac:dyDescent="0.45">
       <c r="A5" s="2" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>39</v>
@@ -1858,7 +1855,7 @@
     </row>
     <row r="6" spans="1:7" ht="216" x14ac:dyDescent="0.45">
       <c r="A6" s="2" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>39</v>
@@ -1880,14 +1877,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G6" xr:uid="{DC1C3C90-61DA-4FB9-8596-D08A0E4C636E}"/>
+  <autoFilter ref="A1:G6" xr:uid="{70B4234C-EC6B-4C15-BA3A-33D9AF79CB16}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B78F4675-43FC-4860-9EAC-039548FB589D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{58FD93CD-A7F0-4C4B-9484-E7BA53B506FE}">
   <dimension ref="A1:G14"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -2015,7 +2012,7 @@
     </row>
     <row r="6" spans="1:7" ht="324" x14ac:dyDescent="0.45">
       <c r="A6" s="2" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>26</v>
@@ -2038,7 +2035,7 @@
     </row>
     <row r="7" spans="1:7" ht="378" x14ac:dyDescent="0.45">
       <c r="A7" s="2" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>26</v>
@@ -2061,7 +2058,7 @@
     </row>
     <row r="8" spans="1:7" ht="378" x14ac:dyDescent="0.45">
       <c r="A8" s="2" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>26</v>
@@ -2084,7 +2081,7 @@
     </row>
     <row r="9" spans="1:7" ht="378" x14ac:dyDescent="0.45">
       <c r="A9" s="2" t="s">
-        <v>44</v>
+        <v>5</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>26</v>
@@ -2107,7 +2104,7 @@
     </row>
     <row r="10" spans="1:7" ht="198" x14ac:dyDescent="0.45">
       <c r="A10" s="2" t="s">
-        <v>5</v>
+        <v>46</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>26</v>
@@ -2119,7 +2116,7 @@
         <v>84</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>85</v>
+        <v>38</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>74</v>
@@ -2130,19 +2127,19 @@
     </row>
     <row r="11" spans="1:7" ht="144" x14ac:dyDescent="0.45">
       <c r="A11" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>39</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>28</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>64</v>
@@ -2153,19 +2150,19 @@
     </row>
     <row r="12" spans="1:7" ht="306" x14ac:dyDescent="0.45">
       <c r="A12" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>39</v>
       </c>
       <c r="C12" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="D12" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="E12" s="2" t="s">
         <v>91</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>92</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>64</v>
@@ -2176,7 +2173,7 @@
     </row>
     <row r="13" spans="1:7" ht="396" x14ac:dyDescent="0.45">
       <c r="A13" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>39</v>
@@ -2185,10 +2182,10 @@
         <v>61</v>
       </c>
       <c r="D13" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>94</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>95</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>64</v>
@@ -2205,10 +2202,10 @@
         <v>39</v>
       </c>
       <c r="C14" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="D14" s="2" t="s">
         <v>96</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>97</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>60</v>
@@ -2221,14 +2218,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G14" xr:uid="{B78F4675-43FC-4860-9EAC-039548FB589D}"/>
+  <autoFilter ref="A1:G14" xr:uid="{58FD93CD-A7F0-4C4B-9484-E7BA53B506FE}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08E2BB7B-6CB3-425F-B888-8A10BB987266}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC93B69F-733E-4FA1-AC2E-189657F288C9}">
   <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -2270,16 +2267,16 @@
         <v>26</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>100</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>101</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>31</v>
@@ -2293,16 +2290,16 @@
         <v>26</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="E3" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="E3" s="2" t="s">
-        <v>104</v>
-      </c>
       <c r="F3" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>31</v>
@@ -2316,16 +2313,16 @@
         <v>26</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="F4" s="2" t="s">
         <v>107</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>108</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>31</v>
@@ -2339,16 +2336,16 @@
         <v>26</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="E5" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="E5" s="2" t="s">
-        <v>111</v>
-      </c>
       <c r="F5" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>31</v>
@@ -2356,36 +2353,36 @@
     </row>
     <row r="6" spans="1:7" ht="216" x14ac:dyDescent="0.45">
       <c r="A6" s="2" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>39</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D6" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="E6" s="2" t="s">
-        <v>113</v>
-      </c>
       <c r="F6" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>31</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G6" xr:uid="{08E2BB7B-6CB3-425F-B888-8A10BB987266}"/>
+  <autoFilter ref="A1:G6" xr:uid="{EC93B69F-733E-4FA1-AC2E-189657F288C9}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{373A4BCC-C738-48E7-8CF4-A1495BD6FD1A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F1DA2375-5859-46E7-BC1E-05D6F0EB3102}">
   <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -2427,16 +2424,16 @@
         <v>26</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>116</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>117</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>31</v>
@@ -2450,16 +2447,16 @@
         <v>26</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="E3" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="F3" s="2" t="s">
         <v>120</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>121</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>31</v>
@@ -2476,27 +2473,27 @@
         <v>31</v>
       </c>
       <c r="D4" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="E4" s="2" t="s">
-        <v>123</v>
-      </c>
       <c r="F4" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>31</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G4" xr:uid="{373A4BCC-C738-48E7-8CF4-A1495BD6FD1A}"/>
+  <autoFilter ref="A1:G4" xr:uid="{F1DA2375-5859-46E7-BC1E-05D6F0EB3102}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCDC749E-B680-416E-A337-277EF4F56C1D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F3027AC-3FE4-4602-9C43-A00ADB999CE0}">
   <dimension ref="A1:G38"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -2538,22 +2535,22 @@
         <v>26</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="F2" s="2" t="s">
-        <v>127</v>
-      </c>
       <c r="G2" s="2" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="306" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:7" ht="288" x14ac:dyDescent="0.45">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
@@ -2561,16 +2558,16 @@
         <v>26</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="F3" s="2" t="s">
         <v>129</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>130</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>31</v>
@@ -2584,16 +2581,16 @@
         <v>26</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="F4" s="2" t="s">
         <v>133</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>134</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>31</v>
@@ -2607,16 +2604,16 @@
         <v>26</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>132</v>
-      </c>
       <c r="E5" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>31</v>
@@ -2624,30 +2621,30 @@
     </row>
     <row r="6" spans="1:7" ht="270" x14ac:dyDescent="0.45">
       <c r="A6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="126" x14ac:dyDescent="0.45">
+      <c r="A7" s="2" t="s">
         <v>15</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="144" x14ac:dyDescent="0.45">
-      <c r="A7" s="2" t="s">
-        <v>8</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>26</v>
@@ -2656,13 +2653,13 @@
         <v>53</v>
       </c>
       <c r="D7" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="F7" s="2" t="s">
         <v>138</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>139</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>31</v>
@@ -2670,22 +2667,22 @@
     </row>
     <row r="8" spans="1:7" ht="180" x14ac:dyDescent="0.45">
       <c r="A8" s="2" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>26</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="E8" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="F8" s="2" t="s">
         <v>142</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>143</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>31</v>
@@ -2693,22 +2690,22 @@
     </row>
     <row r="9" spans="1:7" ht="198" x14ac:dyDescent="0.45">
       <c r="A9" s="2" t="s">
-        <v>44</v>
+        <v>5</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>26</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="E9" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="F9" s="2" t="s">
         <v>146</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>147</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>31</v>
@@ -2716,7 +2713,7 @@
     </row>
     <row r="10" spans="1:7" ht="144" x14ac:dyDescent="0.45">
       <c r="A10" s="2" t="s">
-        <v>5</v>
+        <v>46</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>26</v>
@@ -2725,13 +2722,13 @@
         <v>53</v>
       </c>
       <c r="D10" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="F10" s="2" t="s">
         <v>148</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>149</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>31</v>
@@ -2739,22 +2736,22 @@
     </row>
     <row r="11" spans="1:7" ht="270" x14ac:dyDescent="0.45">
       <c r="A11" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>26</v>
       </c>
       <c r="C11" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="D11" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="E11" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="E11" s="2" t="s">
+      <c r="F11" s="2" t="s">
         <v>152</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>153</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>31</v>
@@ -2762,22 +2759,22 @@
     </row>
     <row r="12" spans="1:7" ht="252" x14ac:dyDescent="0.45">
       <c r="A12" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>26</v>
       </c>
       <c r="C12" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="D12" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="E12" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="E12" s="2" t="s">
-        <v>156</v>
-      </c>
       <c r="F12" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>31</v>
@@ -2785,22 +2782,22 @@
     </row>
     <row r="13" spans="1:7" ht="180" x14ac:dyDescent="0.45">
       <c r="A13" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>26</v>
       </c>
       <c r="C13" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="D13" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="E13" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="E13" s="2" t="s">
-        <v>159</v>
-      </c>
       <c r="F13" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>31</v>
@@ -2814,16 +2811,16 @@
         <v>26</v>
       </c>
       <c r="C14" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="D14" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="E14" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="E14" s="2" t="s">
-        <v>162</v>
-      </c>
       <c r="F14" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>31</v>
@@ -2831,22 +2828,22 @@
     </row>
     <row r="15" spans="1:7" ht="180" x14ac:dyDescent="0.45">
       <c r="A15" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C15" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C15" s="2" t="s">
+      <c r="D15" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="D15" s="2" t="s">
+      <c r="E15" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="E15" s="2" t="s">
-        <v>166</v>
-      </c>
       <c r="F15" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>31</v>
@@ -2854,22 +2851,22 @@
     </row>
     <row r="16" spans="1:7" ht="180" x14ac:dyDescent="0.45">
       <c r="A16" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="B16" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C16" s="2" t="s">
+      <c r="D16" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="D16" s="2" t="s">
+      <c r="E16" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="E16" s="2" t="s">
-        <v>170</v>
-      </c>
       <c r="F16" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>31</v>
@@ -2877,22 +2874,22 @@
     </row>
     <row r="17" spans="1:7" ht="198" x14ac:dyDescent="0.45">
       <c r="A17" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C17" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="B17" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C17" s="2" t="s">
+      <c r="D17" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="D17" s="2" t="s">
+      <c r="E17" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="E17" s="2" t="s">
-        <v>174</v>
-      </c>
       <c r="F17" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>31</v>
@@ -2900,22 +2897,22 @@
     </row>
     <row r="18" spans="1:7" ht="198" x14ac:dyDescent="0.45">
       <c r="A18" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C18" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="B18" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C18" s="2" t="s">
+      <c r="D18" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="D18" s="2" t="s">
+      <c r="E18" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="E18" s="2" t="s">
-        <v>178</v>
-      </c>
       <c r="F18" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>31</v>
@@ -2923,22 +2920,22 @@
     </row>
     <row r="19" spans="1:7" ht="198" x14ac:dyDescent="0.45">
       <c r="A19" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C19" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="B19" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C19" s="2" t="s">
+      <c r="D19" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="D19" s="2" t="s">
+      <c r="E19" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="E19" s="2" t="s">
-        <v>182</v>
-      </c>
       <c r="F19" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>31</v>
@@ -2946,22 +2943,22 @@
     </row>
     <row r="20" spans="1:7" ht="216" x14ac:dyDescent="0.45">
       <c r="A20" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C20" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="B20" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C20" s="2" t="s">
+      <c r="D20" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="D20" s="2" t="s">
+      <c r="E20" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="E20" s="2" t="s">
-        <v>186</v>
-      </c>
       <c r="F20" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>31</v>
@@ -2969,22 +2966,22 @@
     </row>
     <row r="21" spans="1:7" ht="216" x14ac:dyDescent="0.45">
       <c r="A21" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C21" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="B21" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C21" s="2" t="s">
+      <c r="D21" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="D21" s="2" t="s">
+      <c r="E21" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="E21" s="2" t="s">
-        <v>190</v>
-      </c>
       <c r="F21" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>31</v>
@@ -2992,22 +2989,22 @@
     </row>
     <row r="22" spans="1:7" ht="216" x14ac:dyDescent="0.45">
       <c r="A22" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C22" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="B22" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C22" s="2" t="s">
+      <c r="D22" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="D22" s="2" t="s">
+      <c r="E22" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="E22" s="2" t="s">
-        <v>194</v>
-      </c>
       <c r="F22" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>31</v>
@@ -3015,22 +3012,22 @@
     </row>
     <row r="23" spans="1:7" ht="198" x14ac:dyDescent="0.45">
       <c r="A23" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C23" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="B23" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C23" s="2" t="s">
+      <c r="D23" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="D23" s="2" t="s">
+      <c r="E23" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="E23" s="2" t="s">
-        <v>198</v>
-      </c>
       <c r="F23" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>31</v>
@@ -3038,22 +3035,22 @@
     </row>
     <row r="24" spans="1:7" ht="198" x14ac:dyDescent="0.45">
       <c r="A24" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C24" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="B24" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C24" s="2" t="s">
+      <c r="D24" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="D24" s="2" t="s">
+      <c r="E24" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="E24" s="2" t="s">
-        <v>202</v>
-      </c>
       <c r="F24" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>31</v>
@@ -3061,22 +3058,22 @@
     </row>
     <row r="25" spans="1:7" ht="198" x14ac:dyDescent="0.45">
       <c r="A25" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C25" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="B25" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C25" s="2" t="s">
+      <c r="D25" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="D25" s="2" t="s">
+      <c r="E25" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="E25" s="2" t="s">
-        <v>206</v>
-      </c>
       <c r="F25" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>31</v>
@@ -3084,22 +3081,22 @@
     </row>
     <row r="26" spans="1:7" ht="342" x14ac:dyDescent="0.45">
       <c r="A26" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C26" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="B26" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C26" s="2" t="s">
+      <c r="D26" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="D26" s="2" t="s">
+      <c r="E26" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="E26" s="2" t="s">
-        <v>210</v>
-      </c>
       <c r="F26" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>31</v>
@@ -3107,22 +3104,22 @@
     </row>
     <row r="27" spans="1:7" ht="198" x14ac:dyDescent="0.45">
       <c r="A27" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C27" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="B27" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C27" s="2" t="s">
+      <c r="D27" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="D27" s="2" t="s">
+      <c r="E27" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="E27" s="2" t="s">
-        <v>214</v>
-      </c>
       <c r="F27" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>31</v>
@@ -3130,22 +3127,22 @@
     </row>
     <row r="28" spans="1:7" ht="252" x14ac:dyDescent="0.45">
       <c r="A28" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C28" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="B28" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C28" s="2" t="s">
+      <c r="D28" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="D28" s="2" t="s">
+      <c r="E28" s="2" t="s">
         <v>217</v>
       </c>
-      <c r="E28" s="2" t="s">
-        <v>218</v>
-      </c>
       <c r="F28" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>31</v>
@@ -3153,22 +3150,22 @@
     </row>
     <row r="29" spans="1:7" ht="198" x14ac:dyDescent="0.45">
       <c r="A29" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C29" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="B29" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C29" s="2" t="s">
+      <c r="D29" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="D29" s="2" t="s">
+      <c r="E29" s="2" t="s">
         <v>221</v>
       </c>
-      <c r="E29" s="2" t="s">
-        <v>222</v>
-      </c>
       <c r="F29" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>31</v>
@@ -3176,22 +3173,22 @@
     </row>
     <row r="30" spans="1:7" ht="198" x14ac:dyDescent="0.45">
       <c r="A30" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>39</v>
       </c>
       <c r="C30" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="E30" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="D30" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>225</v>
-      </c>
       <c r="F30" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>31</v>
@@ -3199,7 +3196,7 @@
     </row>
     <row r="31" spans="1:7" ht="216" x14ac:dyDescent="0.45">
       <c r="A31" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>39</v>
@@ -3208,13 +3205,13 @@
         <v>53</v>
       </c>
       <c r="D31" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="E31" s="2" t="s">
         <v>227</v>
       </c>
-      <c r="E31" s="2" t="s">
-        <v>228</v>
-      </c>
       <c r="F31" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>31</v>
@@ -3222,22 +3219,22 @@
     </row>
     <row r="32" spans="1:7" ht="234" x14ac:dyDescent="0.45">
       <c r="A32" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>39</v>
       </c>
       <c r="C32" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="D32" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="D32" s="2" t="s">
+      <c r="E32" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="E32" s="2" t="s">
-        <v>232</v>
-      </c>
       <c r="F32" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>31</v>
@@ -3245,22 +3242,22 @@
     </row>
     <row r="33" spans="1:7" ht="270" x14ac:dyDescent="0.45">
       <c r="A33" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>39</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>31</v>
@@ -3268,22 +3265,22 @@
     </row>
     <row r="34" spans="1:7" ht="306" x14ac:dyDescent="0.45">
       <c r="A34" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>39</v>
       </c>
       <c r="C34" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="E34" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="D34" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>237</v>
-      </c>
       <c r="F34" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>31</v>
@@ -3291,22 +3288,22 @@
     </row>
     <row r="35" spans="1:7" ht="234" x14ac:dyDescent="0.45">
       <c r="A35" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>39</v>
       </c>
       <c r="C35" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="D35" s="2" t="s">
         <v>239</v>
       </c>
-      <c r="D35" s="2" t="s">
+      <c r="E35" s="2" t="s">
         <v>240</v>
       </c>
-      <c r="E35" s="2" t="s">
-        <v>241</v>
-      </c>
       <c r="F35" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>31</v>
@@ -3314,22 +3311,22 @@
     </row>
     <row r="36" spans="1:7" ht="234" x14ac:dyDescent="0.45">
       <c r="A36" s="2" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>39</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D36" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="E36" s="2" t="s">
         <v>240</v>
       </c>
-      <c r="E36" s="2" t="s">
-        <v>241</v>
-      </c>
       <c r="F36" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>31</v>
@@ -3337,22 +3334,22 @@
     </row>
     <row r="37" spans="1:7" ht="198" x14ac:dyDescent="0.45">
       <c r="A37" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>39</v>
       </c>
       <c r="C37" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="E37" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="D37" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="E37" s="2" t="s">
-        <v>246</v>
-      </c>
       <c r="F37" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>31</v>
@@ -3360,36 +3357,36 @@
     </row>
     <row r="38" spans="1:7" ht="252" x14ac:dyDescent="0.45">
       <c r="A38" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>39</v>
       </c>
       <c r="C38" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="D38" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="D38" s="2" t="s">
-        <v>248</v>
-      </c>
       <c r="E38" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="G38" s="2" t="s">
         <v>31</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G38" xr:uid="{DCDC749E-B680-416E-A337-277EF4F56C1D}"/>
+  <autoFilter ref="A1:G38" xr:uid="{8F3027AC-3FE4-4602-9C43-A00ADB999CE0}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF7D0ABF-F9AF-49BD-9DD2-11F2377E8538}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C57156E-516B-40CD-A8FC-971ADBE9AFCE}">
   <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -3437,10 +3434,10 @@
         <v>28</v>
       </c>
       <c r="E2" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>249</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>250</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>31</v>
@@ -3460,10 +3457,10 @@
         <v>28</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>31</v>
@@ -3483,10 +3480,10 @@
         <v>54</v>
       </c>
       <c r="E4" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>252</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>253</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>31</v>
@@ -3500,7 +3497,7 @@
         <v>39</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>28</v>
@@ -3509,14 +3506,14 @@
         <v>60</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>31</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G5" xr:uid="{FF7D0ABF-F9AF-49BD-9DD2-11F2377E8538}"/>
+  <autoFilter ref="A1:G5" xr:uid="{7C57156E-516B-40CD-A8FC-971ADBE9AFCE}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/tool/package-generator/doc/03_結合テスト/テスト仕様書.xlsx
+++ b/tool/package-generator/doc/03_結合テスト/テスト仕様書.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\myrepo\project_management\tool\package-generator\doc\03_結合テスト\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6772E09E-FADE-4BAA-9459-181865FF2071}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6EC983E1-03E4-4E79-A95E-934D59AE6019}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{2326F0BB-6FE5-4BBE-811B-37C5A426EA4C}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{2F3AECA2-21E7-4B31-A08A-25B4E6E915AB}"/>
   </bookViews>
   <sheets>
     <sheet name="一覧" sheetId="1" r:id="rId1"/>
@@ -163,9 +163,7 @@
     <t>「対象のグループ」を設定した後で、「実行」を押した後で、「開く（パッケージの作成）」を押します。</t>
   </si>
   <si>
-    <t>開く（パッケージの作成）：出力先のフォルダ
-状態（パッケージの作成）：成功または警告
-状態：成功または警告</t>
+    <t>開く（パッケージの作成）：出力先のフォルダ</t>
   </si>
   <si>
     <t>「対象のグループ」を設定した後で、「実行」を押した後で、「開く（パッケージのアップロード）」を押します。</t>
@@ -625,14 +623,14 @@
   </si>
   <si>
     <t>対象のグループ：ok
-ログイン名：テスト用の値
+ログイン名：saved-login
 設定ファイル：ok.bat</t>
   </si>
   <si>
     <t>「対象のグループ」と「ログイン名」を設定した後で、「保存」を押します。</t>
   </si>
   <si>
-    <t>設定ファイル：ok.bat の KintoneLoginName が保存される
+    <t>設定ファイル：ok.bat に KintoneLoginName=saved-login が保存される
 状態（保存）：完了</t>
   </si>
   <si>
@@ -653,14 +651,14 @@
   </si>
   <si>
     <t>対象のグループ：ok
-パスワード：テスト用の値
+パスワード：saved-pass
 設定ファイル：ok.bat</t>
   </si>
   <si>
     <t>「対象のグループ」と「パスワード」を設定した後で、「保存」を押します。</t>
   </si>
   <si>
-    <t>設定ファイル：ok.bat の KintonePassword が保存される
+    <t>設定ファイル：ok.bat に KintonePassword=saved-pass が保存される
 状態（保存）：完了</t>
   </si>
   <si>
@@ -675,7 +673,7 @@
     <t>「対象のグループ」と「対象アプリID」を設定した後で、「保存」を押します。</t>
   </si>
   <si>
-    <t>設定ファイル：ok.bat に saved-app-id が保存される
+    <t>設定ファイル：ok.bat に TargetAppId=saved-app-id が保存される
 状態（保存）：完了</t>
   </si>
   <si>
@@ -706,7 +704,7 @@
     <t>「対象のグループ」と「圧縮元のフォルダ」を設定した後で、「保存」を押します。</t>
   </si>
   <si>
-    <t>設定ファイル：ok.bat に saved-source が保存される
+    <t>設定ファイル：ok.bat に GenerateSourcePath=saved-source が保存される
 状態（保存）：完了</t>
   </si>
   <si>
@@ -737,7 +735,7 @@
     <t>「対象のグループ」と「パッケージ定義ファイル」を設定した後で、「保存」を押します。</t>
   </si>
   <si>
-    <t>設定ファイル：ok.bat に saved-config が保存される
+    <t>設定ファイル：ok.bat に GenerateConfigPath=saved-config が保存される
 状態（保存）：完了</t>
   </si>
   <si>
@@ -768,7 +766,7 @@
     <t>「対象のグループ」と「作業用のフォルダ」を設定した後で、「保存」を押します。</t>
   </si>
   <si>
-    <t>設定ファイル：ok.bat に saved-work-folder が保存される
+    <t>設定ファイル：ok.bat に GenerateWorkPath=saved-work-folder が保存される
 状態（保存）：完了</t>
   </si>
   <si>
@@ -799,7 +797,7 @@
     <t>「対象のグループ」と「パッケージの出力先」を設定した後で、「保存」を押します。</t>
   </si>
   <si>
-    <t>設定ファイル：ok.bat に saved-output が保存される
+    <t>設定ファイル：ok.bat に GenerateOutputPath=saved-output が保存される
 状態（保存）：完了</t>
   </si>
   <si>
@@ -1397,7 +1395,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB06E082-9175-4E30-A834-E0E870E3199E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E18A4D8B-9D65-4EE2-AA30-F5B4DCFECD45}">
   <dimension ref="A1:C8"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -1494,14 +1492,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C8" xr:uid="{EB06E082-9175-4E30-A834-E0E870E3199E}"/>
+  <autoFilter ref="A1:C8" xr:uid="{E18A4D8B-9D65-4EE2-AA30-F5B4DCFECD45}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7DCBCEF-0881-4966-9558-FA97634E44A6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B290496-678A-40D6-A6B5-58059700DDF7}">
   <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -1581,7 +1579,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="270" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:7" ht="234" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
         <v>12</v>
       </c>
@@ -1720,14 +1718,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G9" xr:uid="{A7DCBCEF-0881-4966-9558-FA97634E44A6}"/>
+  <autoFilter ref="A1:G9" xr:uid="{0B290496-678A-40D6-A6B5-58059700DDF7}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70B4234C-EC6B-4C15-BA3A-33D9AF79CB16}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F4BA221-E450-428F-ABDF-4C293A3CD968}">
   <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -1877,14 +1875,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G6" xr:uid="{70B4234C-EC6B-4C15-BA3A-33D9AF79CB16}"/>
+  <autoFilter ref="A1:G6" xr:uid="{3F4BA221-E450-428F-ABDF-4C293A3CD968}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{58FD93CD-A7F0-4C4B-9484-E7BA53B506FE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B122FD7-04DF-4ABF-84C9-EC51E834E480}">
   <dimension ref="A1:G14"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -2218,14 +2216,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G14" xr:uid="{58FD93CD-A7F0-4C4B-9484-E7BA53B506FE}"/>
+  <autoFilter ref="A1:G14" xr:uid="{2B122FD7-04DF-4ABF-84C9-EC51E834E480}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC93B69F-733E-4FA1-AC2E-189657F288C9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6130A7DE-650E-4005-B97C-C13385819BE2}">
   <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -2375,14 +2373,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G6" xr:uid="{EC93B69F-733E-4FA1-AC2E-189657F288C9}"/>
+  <autoFilter ref="A1:G6" xr:uid="{6130A7DE-650E-4005-B97C-C13385819BE2}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F1DA2375-5859-46E7-BC1E-05D6F0EB3102}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96F81835-F617-477B-8B55-EC0378AB47E1}">
   <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -2486,14 +2484,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G4" xr:uid="{F1DA2375-5859-46E7-BC1E-05D6F0EB3102}"/>
+  <autoFilter ref="A1:G4" xr:uid="{96F81835-F617-477B-8B55-EC0378AB47E1}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F3027AC-3FE4-4602-9C43-A00ADB999CE0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD9642D5-48A9-4471-A89C-5759095AEDE4}">
   <dimension ref="A1:G38"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -2780,7 +2778,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="180" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:7" ht="198" x14ac:dyDescent="0.45">
       <c r="A13" s="2" t="s">
         <v>92</v>
       </c>
@@ -2826,7 +2824,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="180" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:7" ht="198" x14ac:dyDescent="0.45">
       <c r="A15" s="2" t="s">
         <v>162</v>
       </c>
@@ -2849,7 +2847,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="180" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:7" ht="198" x14ac:dyDescent="0.45">
       <c r="A16" s="2" t="s">
         <v>166</v>
       </c>
@@ -2895,7 +2893,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="198" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:7" ht="216" x14ac:dyDescent="0.45">
       <c r="A18" s="2" t="s">
         <v>174</v>
       </c>
@@ -2987,7 +2985,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="216" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:7" ht="234" x14ac:dyDescent="0.45">
       <c r="A22" s="2" t="s">
         <v>190</v>
       </c>
@@ -3033,7 +3031,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="198" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:7" ht="216" x14ac:dyDescent="0.45">
       <c r="A24" s="2" t="s">
         <v>198</v>
       </c>
@@ -3379,14 +3377,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G38" xr:uid="{8F3027AC-3FE4-4602-9C43-A00ADB999CE0}"/>
+  <autoFilter ref="A1:G38" xr:uid="{BD9642D5-48A9-4471-A89C-5759095AEDE4}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C57156E-516B-40CD-A8FC-971ADBE9AFCE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5CA316CD-706E-4512-8F44-EBE1A8C3D97C}">
   <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -3513,7 +3511,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G5" xr:uid="{7C57156E-516B-40CD-A8FC-971ADBE9AFCE}"/>
+  <autoFilter ref="A1:G5" xr:uid="{5CA316CD-706E-4512-8F44-EBE1A8C3D97C}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/tool/package-generator/doc/03_結合テスト/テスト仕様書.xlsx
+++ b/tool/package-generator/doc/03_結合テスト/テスト仕様書.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\myrepo\project_management\tool\package-generator\doc\03_結合テスト\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6EC983E1-03E4-4E79-A95E-934D59AE6019}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{84E25636-5AF9-465B-96D5-45FE2800C045}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{2F3AECA2-21E7-4B31-A08A-25B4E6E915AB}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{3999D35C-2E54-4CB8-9927-2ACCDF63C906}"/>
   </bookViews>
   <sheets>
     <sheet name="一覧" sheetId="1" r:id="rId1"/>
@@ -1395,7 +1395,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E18A4D8B-9D65-4EE2-AA30-F5B4DCFECD45}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D8E0B21-724C-4E4D-A6E0-152F39C9F67B}">
   <dimension ref="A1:C8"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -1492,14 +1492,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C8" xr:uid="{E18A4D8B-9D65-4EE2-AA30-F5B4DCFECD45}"/>
+  <autoFilter ref="A1:C8" xr:uid="{9D8E0B21-724C-4E4D-A6E0-152F39C9F67B}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B290496-678A-40D6-A6B5-58059700DDF7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B4889EF-6408-405D-8680-A223B04F8382}">
   <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -1718,14 +1718,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G9" xr:uid="{0B290496-678A-40D6-A6B5-58059700DDF7}"/>
+  <autoFilter ref="A1:G9" xr:uid="{5B4889EF-6408-405D-8680-A223B04F8382}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F4BA221-E450-428F-ABDF-4C293A3CD968}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6D56C1B-F250-4500-8B5A-07127B157EB4}">
   <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -1875,14 +1875,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G6" xr:uid="{3F4BA221-E450-428F-ABDF-4C293A3CD968}"/>
+  <autoFilter ref="A1:G6" xr:uid="{B6D56C1B-F250-4500-8B5A-07127B157EB4}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B122FD7-04DF-4ABF-84C9-EC51E834E480}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B4A2E79-1981-40C0-8F81-3581C5C7CB59}">
   <dimension ref="A1:G14"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -2216,14 +2216,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G14" xr:uid="{2B122FD7-04DF-4ABF-84C9-EC51E834E480}"/>
+  <autoFilter ref="A1:G14" xr:uid="{9B4A2E79-1981-40C0-8F81-3581C5C7CB59}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6130A7DE-650E-4005-B97C-C13385819BE2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{696268B0-D2E8-48C7-82C1-B2E767FCC236}">
   <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -2373,14 +2373,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G6" xr:uid="{6130A7DE-650E-4005-B97C-C13385819BE2}"/>
+  <autoFilter ref="A1:G6" xr:uid="{696268B0-D2E8-48C7-82C1-B2E767FCC236}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96F81835-F617-477B-8B55-EC0378AB47E1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A3B333B-F7D4-41E0-8E5A-5356CD146E58}">
   <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -2484,14 +2484,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G4" xr:uid="{96F81835-F617-477B-8B55-EC0378AB47E1}"/>
+  <autoFilter ref="A1:G4" xr:uid="{3A3B333B-F7D4-41E0-8E5A-5356CD146E58}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD9642D5-48A9-4471-A89C-5759095AEDE4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24C51438-C5C8-4633-83DD-AB8CAB450C2D}">
   <dimension ref="A1:G38"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -3377,14 +3377,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G38" xr:uid="{BD9642D5-48A9-4471-A89C-5759095AEDE4}"/>
+  <autoFilter ref="A1:G38" xr:uid="{24C51438-C5C8-4633-83DD-AB8CAB450C2D}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5CA316CD-706E-4512-8F44-EBE1A8C3D97C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F35AD59-A05A-42FC-BDBC-146184D11439}">
   <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -3511,7 +3511,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G5" xr:uid="{5CA316CD-706E-4512-8F44-EBE1A8C3D97C}"/>
+  <autoFilter ref="A1:G5" xr:uid="{9F35AD59-A05A-42FC-BDBC-146184D11439}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/tool/package-generator/doc/03_結合テスト/テスト仕様書.xlsx
+++ b/tool/package-generator/doc/03_結合テスト/テスト仕様書.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\myrepo\project_management\tool\package-generator\doc\03_結合テスト\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{84E25636-5AF9-465B-96D5-45FE2800C045}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CE0578A4-38A1-4297-AA57-B0E0F4717D83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{3999D35C-2E54-4CB8-9927-2ACCDF63C906}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B156AF56-52F7-4CC9-9700-BA1BAF776B7E}"/>
   </bookViews>
   <sheets>
     <sheet name="一覧" sheetId="1" r:id="rId1"/>
@@ -23,12 +23,12 @@
     <sheet name="2.7 環境設定（パッケージ定義）" sheetId="8" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2.1 実行（一括実行）'!$A$1:$G$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2.1 実行（一括実行）'!$A$1:$G$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'2.2 実行（パッケージ作成）'!$A$1:$G$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'2.3 実行（パッケージ反映）'!$A$1:$G$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'2.3 実行（パッケージ反映）'!$A$1:$G$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'2.4 ログ'!$A$1:$G$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'2.5 環境設定（共通）'!$A$1:$G$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'2.6 環境設定（グループ別）'!$A$1:$G$38</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'2.6 環境設定（グループ別）'!$A$1:$G$37</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'2.7 環境設定（パッケージ定義）'!$A$1:$G$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">一覧!$A$1:$C$8</definedName>
   </definedNames>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="598" uniqueCount="254">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="577" uniqueCount="248">
   <si>
     <t>通番</t>
   </si>
@@ -177,24 +177,12 @@
   <si>
     <t>対象のグループ：ng
 タイトル：空
-フォルダ：空
 パッケージの作成：あり
 パッケージのアップロード：あり
 設定ファイル：ng.bat</t>
   </si>
   <si>
     <t>メッセージ：「タイトル を設定してください。」</t>
-  </si>
-  <si>
-    <t>対象のグループ：ng
-タイトル：TestTitle
-フォルダ：空
-パッケージの作成：あり
-パッケージのアップロード：あり
-設定ファイル：ng.bat</t>
-  </si>
-  <si>
-    <t>メッセージ：「フォルダ を設定してください。」</t>
   </si>
   <si>
     <t>対象のグループ：ng（圧縮元のフォルダがない）
@@ -208,9 +196,6 @@
 状態：失敗</t>
   </si>
   <si>
-    <t>9</t>
-  </si>
-  <si>
     <t>対象のグループ：ng
 パッケージの作成：なし
 パッケージのアップロード：あり
@@ -271,7 +256,7 @@
 設定ファイル：ok.bat</t>
   </si>
   <si>
-    <t>「実行（パッケージ作成）」を実行し、「実行（パッケージ反映）」で「対象のグループ」を設定し、「クリア（フォルダ）」を押した後で、「タイトル」と「ファイル1」を設定した後で、「実行」を押します。</t>
+    <t>「実行（パッケージ作成）」を実行し、「実行（パッケージ反映）」で「対象のグループ」を設定し、「タイトル」と「ファイル1」を設定した後で、「実行」を押します。</t>
   </si>
   <si>
     <t>状態：成功
@@ -284,14 +269,14 @@
   <si>
     <t>対象のグループ：ok
 タイトル：TestTitle
-フォルダ：入力なし（画面に入っている値のまま）
+ファイル1〜3：入力なし（既定の出力先の zip を使う）
 設定ファイル：ok.bat</t>
   </si>
   <si>
     <t>「実行（パッケージ作成）」を実行し、「実行（パッケージ反映）」で「対象のグループ」と「タイトル」を設定した後で、「実行」を押します。</t>
   </si>
   <si>
-    <t>「実行（パッケージ作成）」を実行し、「実行（パッケージ反映）」で「対象のグループ」を設定し、「クリア（フォルダ）」を押した後で、「タイトル」と「ファイル1」を設定した後で、「実行」を押した後で、「実行」を押します。</t>
+    <t>「実行（パッケージ作成）」を実行し、「実行（パッケージ反映）」で「対象のグループ」を設定し、「タイトル」と「ファイル1」を設定した後で、「実行」を押した後で、「実行」を押します。</t>
   </si>
   <si>
     <t>状態：成功
@@ -306,31 +291,25 @@
 設定ファイル：ok.bat</t>
   </si>
   <si>
-    <t>「実行（パッケージ作成）」を実行し、「実行（パッケージ反映）」で「対象のグループ」を設定し、「クリア（フォルダ）」を押した後で、「タイトル」と「ファイル1」と「説明」を設定した後で、「実行」を押します。</t>
+    <t>「実行（パッケージ作成）」を実行し、「実行（パッケージ反映）」で「対象のグループ」を設定し、「タイトル」と「ファイル1」と「説明」を設定した後で、「実行」を押します。</t>
   </si>
   <si>
     <t>状態：成功
 ログ：入力した説明が入る</t>
   </si>
   <si>
-    <t>「実行（パッケージ作成）」を実行し、「実行（パッケージ反映）」で「対象のグループ」を設定し、「クリア（フォルダ）」を押します。</t>
-  </si>
-  <si>
-    <t>フォルダ：空</t>
-  </si>
-  <si>
-    <t>画面設計：3.3</t>
-  </si>
-  <si>
     <t>対象のグループ：ok
 ファイル1：コースA.zip
 設定ファイル：ok.bat</t>
   </si>
   <si>
-    <t>「実行（パッケージ作成）」を実行し、「実行（パッケージ反映）」で「対象のグループ」と「ファイル1」を設定した後で、「クリア（ファイル1）」を押します。</t>
+    <t>「実行（パッケージ反映）」で「対象のグループ」と「ファイル1」を設定した後で、「クリア（ファイル1）」を押します。</t>
   </si>
   <si>
     <t>ファイル1：空</t>
+  </si>
+  <si>
+    <t>画面設計：3.3</t>
   </si>
   <si>
     <t>対象のグループ：ok
@@ -338,7 +317,7 @@
 設定ファイル：ok.bat</t>
   </si>
   <si>
-    <t>「実行（パッケージ作成）」を実行し、「実行（パッケージ反映）」で「対象のグループ」と「ファイル2」を設定した後で、「クリア（ファイル2）」を押します。</t>
+    <t>「実行（パッケージ反映）」で「対象のグループ」と「ファイル2」を設定した後で、「クリア（ファイル2）」を押します。</t>
   </si>
   <si>
     <t>ファイル2：空</t>
@@ -349,7 +328,7 @@
 設定ファイル：ok.bat</t>
   </si>
   <si>
-    <t>「実行（パッケージ作成）」を実行し、「実行（パッケージ反映）」で「対象のグループ」と「ファイル3」を設定した後で、「クリア（ファイル3）」を押します。</t>
+    <t>「実行（パッケージ反映）」で「対象のグループ」と「ファイル3」を設定した後で、「クリア（ファイル3）」を押します。</t>
   </si>
   <si>
     <t>ファイル3：空</t>
@@ -358,26 +337,25 @@
     <t>「実行（パッケージ反映）」で「対象のグループ」を設定した後で、「開く」を押します。</t>
   </si>
   <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>対象のグループ：ok
+タイトル：空
+設定ファイル：ok.bat</t>
+  </si>
+  <si>
+    <t>メッセージ：「タイトルを入力してください」</t>
+  </si>
+  <si>
     <t>10</t>
   </si>
   <si>
-    <t>対象のグループ：ng
-タイトル：空
-設定ファイル：ng.bat</t>
-  </si>
-  <si>
-    <t>メッセージ：「タイトルを入力してください」</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>対象のグループ：ng
+    <t>対象のグループ：ok
 タイトル：TestTitle
-フォルダ：空
 ファイル1：空
 ファイル2：空
-ファイル3：空
+ファイル3：空（既定の出力先に zip がない）
 設定ファイル：ng.bat</t>
   </si>
   <si>
@@ -387,13 +365,13 @@
     <t>メッセージ：「zipファイルを1つ以上指定してください」</t>
   </si>
   <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>メッセージ：「同じ名前のzipファイルがあります」</t>
+  </si>
+  <si>
     <t>12</t>
-  </si>
-  <si>
-    <t>「実行（パッケージ作成）」を実行し、「実行（パッケージ反映）」で「対象のグループ」を設定し、「タイトル」と「ファイル1」を設定した後で、「実行」を押します。</t>
-  </si>
-  <si>
-    <t>メッセージ：「同じ名前のzipファイルがあります」</t>
   </si>
   <si>
     <t>対象のグループ：ng
@@ -468,7 +446,7 @@
     <t>「ログの出力先」を設定した後で、「保存」を押します。</t>
   </si>
   <si>
-    <t>設定ファイル（common.bat）：CommonLogPath=saved-log-path が保存される
+    <t>設定ファイル：common.batにCommonLogPath=saved-log-path が保存される
 状態（保存）：完了</t>
   </si>
   <si>
@@ -515,7 +493,8 @@
   </si>
   <si>
     <t>状態（保存）：完了
-ファイル：TestNew.bat に KintoneSubdomain=univ-kyousai-{x} が保存される、TestNew.xlsx</t>
+設定ファイル：TestNew.bat に KintoneSubdomain=univ-kyousai-{x} が保存される
+定義ファイル：TestNew.xlsx</t>
   </si>
   <si>
     <t>画面設計：3.6
@@ -525,7 +504,7 @@
   <si>
     <t>対象のグループ：ok
 設定ファイル：ok.bat
-Excel ファイル：ok.xlsx
+定義ファイル：ok.xlsx
 グループ名：TestCopy</t>
   </si>
   <si>
@@ -533,24 +512,21 @@
   </si>
   <si>
     <t>一覧：TestCopy が追加される
-ファイル：TestCopy.bat と TestCopy.xlsx</t>
+設定ファイル：TestCopy.bat
+定義ファイル：TestCopy.xlsx</t>
   </si>
   <si>
     <t>画面設計：3.6
 処理フロー：2.8</t>
   </si>
   <si>
-    <t>ok.bat の内容：generated\ok を含む
-ok.xlsx：残る</t>
-  </si>
-  <si>
-    <t>ファイル：TestCopy.bat の内容：TestCopy を含む（パッケージの出力先の名前が新しいグループの名前になる）</t>
+    <t>設定ファイル：TestCopy.bat の内容：TestCopy を含む（パッケージの出力先の名前が新しいグループの名前になる）</t>
   </si>
   <si>
     <t>「対象のグループ」を設定した後で、「開く」を押します。</t>
   </si>
   <si>
-    <t>開く：対象のグループの Excel ファイル（ok.xlsx）</t>
+    <t>開く：対象のグループの 定義ファイル（ok.xlsx）</t>
   </si>
   <si>
     <t>画面設計：3.6</t>
@@ -594,13 +570,13 @@
     <t>対象のグループ：ok
 サブドメイン：saved-subdomain
 設定ファイル：ok.bat
-Excel ファイル：ok.xlsx</t>
+定義ファイル：ok.xlsx</t>
   </si>
   <si>
     <t>「対象のグループ」と「サブドメイン」を設定した後で、「保存」を押します。</t>
   </si>
   <si>
-    <t>設定ファイル（ok.bat）：KintoneSubdomain=saved-subdomain が保存される
+    <t>設定ファイル：ok.batにKintoneSubdomain=saved-subdomain が保存される
 状態（保存）：完了</t>
   </si>
   <si>
@@ -611,7 +587,7 @@
     <t>対象のグループ：ok
 サブドメイン：tmp-reload
 設定ファイル：ok.bat
-Excel ファイル：ok.xlsx</t>
+定義ファイル：ok.xlsx</t>
   </si>
   <si>
     <t>「対象のグループ」と「サブドメイン」を設定した後で、「再読込」を押します。</t>
@@ -647,9 +623,6 @@
 状態（再読込）：完了</t>
   </si>
   <si>
-    <t>14</t>
-  </si>
-  <si>
     <t>対象のグループ：ok
 パスワード：saved-pass
 設定ファイル：ok.bat</t>
@@ -662,7 +635,7 @@
 状態（保存）：完了</t>
   </si>
   <si>
-    <t>15</t>
+    <t>14</t>
   </si>
   <si>
     <t>対象のグループ：ok
@@ -677,7 +650,7 @@
 状態（保存）：完了</t>
   </si>
   <si>
-    <t>16</t>
+    <t>15</t>
   </si>
   <si>
     <t>対象のグループ：ok
@@ -693,7 +666,7 @@
 状態（再読込）：完了</t>
   </si>
   <si>
-    <t>17</t>
+    <t>16</t>
   </si>
   <si>
     <t>対象のグループ：ok
@@ -708,7 +681,7 @@
 状態（保存）：完了</t>
   </si>
   <si>
-    <t>18</t>
+    <t>17</t>
   </si>
   <si>
     <t>対象のグループ：ok
@@ -724,7 +697,7 @@
 状態（再読込）：完了</t>
   </si>
   <si>
-    <t>19</t>
+    <t>18</t>
   </si>
   <si>
     <t>対象のグループ：ok
@@ -739,7 +712,7 @@
 状態（保存）：完了</t>
   </si>
   <si>
-    <t>20</t>
+    <t>19</t>
   </si>
   <si>
     <t>対象のグループ：ok
@@ -755,7 +728,7 @@
 状態（再読込）：完了</t>
   </si>
   <si>
-    <t>21</t>
+    <t>20</t>
   </si>
   <si>
     <t>対象のグループ：ok
@@ -770,7 +743,7 @@
 状態（保存）：完了</t>
   </si>
   <si>
-    <t>22</t>
+    <t>21</t>
   </si>
   <si>
     <t>対象のグループ：ok
@@ -786,7 +759,7 @@
 状態（再読込）：完了</t>
   </si>
   <si>
-    <t>23</t>
+    <t>22</t>
   </si>
   <si>
     <t>対象のグループ：ok
@@ -801,7 +774,7 @@
 状態（保存）：完了</t>
   </si>
   <si>
-    <t>24</t>
+    <t>23</t>
   </si>
   <si>
     <t>対象のグループ：ok
@@ -817,7 +790,7 @@
 状態（再読込）：完了</t>
   </si>
   <si>
-    <t>25</t>
+    <t>24</t>
   </si>
   <si>
     <t>対象のグループ：ok、ng、ok
@@ -828,12 +801,12 @@
     <t>「対象のグループ」と「対象のシート」を設定した後で、「保存」を押した後で、「対象のグループ」を設定し直します。</t>
   </si>
   <si>
-    <t>設定ファイル（ok.bat）：GenerateSheetsInclude=saved-sheets が保存される
+    <t>設定ファイル：ok.batにGenerateSheetsInclude=saved-sheets が保存される
 状態（保存）：完了
 対象のシート：saved-sheets が残る</t>
   </si>
   <si>
-    <t>26</t>
+    <t>25</t>
   </si>
   <si>
     <t>対象のグループ：ok
@@ -849,7 +822,7 @@
 状態（再読込）：完了</t>
   </si>
   <si>
-    <t>27</t>
+    <t>26</t>
   </si>
   <si>
     <t>対象のグループ：ok
@@ -864,7 +837,7 @@
 状態（保存）：完了</t>
   </si>
   <si>
-    <t>28</t>
+    <t>27</t>
   </si>
   <si>
     <t>対象のグループ：ok
@@ -880,7 +853,7 @@
 状態（再読込）：完了</t>
   </si>
   <si>
-    <t>29</t>
+    <t>28</t>
   </si>
   <si>
     <t>対象のグループ：ok
@@ -891,16 +864,16 @@
     <t>メッセージ：「（入力した名前）は既に存在します。」</t>
   </si>
   <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>「対象のグループ」を設定した後で、「新規作成」を押した後で、「キャンセル」を押します。</t>
+  </si>
+  <si>
+    <t>設定ファイル：TestCancel.bat が作られない</t>
+  </si>
+  <si>
     <t>30</t>
-  </si>
-  <si>
-    <t>「対象のグループ」を設定した後で、「新規作成」を押した後で、「キャンセル」を押します。</t>
-  </si>
-  <si>
-    <t>ファイル：TestCancel.bat が作られない</t>
-  </si>
-  <si>
-    <t>31</t>
   </si>
   <si>
     <t>対象のグループ：ok
@@ -912,19 +885,19 @@
   </si>
   <si>
     <t>メッセージ：「コピー元のグループが存在しません。」
-ファイル：TestUnsaved.bat が作られない</t>
+設定ファイル：TestUnsaved.bat が作られない</t>
+  </si>
+  <si>
+    <t>31</t>
+  </si>
+  <si>
+    <t>対象のグループ：ok
+設定ファイル：ok.bat
+定義ファイル：ok.xlsx
+グループ名：ok（既存のグループ名）</t>
   </si>
   <si>
     <t>32</t>
-  </si>
-  <si>
-    <t>対象のグループ：ok
-設定ファイル：ok.bat
-Excel ファイル：ok.xlsx
-グループ名：ok（既存のグループ名）</t>
-  </si>
-  <si>
-    <t>33</t>
   </si>
   <si>
     <t>対象のグループ：ok
@@ -936,7 +909,7 @@
 状態（認証情報）：失敗</t>
   </si>
   <si>
-    <t>34</t>
+    <t>33</t>
   </si>
   <si>
     <t>対象のグループ：ok
@@ -950,7 +923,7 @@
     <t>状態（認証情報）：失敗</t>
   </si>
   <si>
-    <t>35</t>
+    <t>34</t>
   </si>
   <si>
     <t>対象のグループ：ng
@@ -958,7 +931,7 @@
 設定ファイル：ng.bat</t>
   </si>
   <si>
-    <t>36</t>
+    <t>35</t>
   </si>
   <si>
     <t>対象のグループ：ok
@@ -969,6 +942,9 @@
     <t>状態（ファイル管理）：失敗</t>
   </si>
   <si>
+    <t>36</t>
+  </si>
+  <si>
     <t>対象のグループ：ok
 対象アプリID：99999999
 設定ファイル：ok.bat</t>
@@ -985,7 +961,7 @@
   </si>
   <si>
     <t>状態：成功
-テンプレートシートの A2：書き換えられる（MARKER_ROW2 のままではなく、空でもない）</t>
+テンプレートシート：書き換えられる</t>
   </si>
   <si>
     <t>開く：更新されたパッケージ定義ファイル（ok.xlsx）</t>
@@ -1395,7 +1371,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D8E0B21-724C-4E4D-A6E0-152F39C9F67B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A99E2F7-CF49-4B4B-BC35-7F152AE9254B}">
   <dimension ref="A1:C8"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -1492,15 +1468,15 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C8" xr:uid="{9D8E0B21-724C-4E4D-A6E0-152F39C9F67B}"/>
+  <autoFilter ref="A1:C8" xr:uid="{1A99E2F7-CF49-4B4B-BC35-7F152AE9254B}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B4889EF-6408-405D-8680-A223B04F8382}">
-  <dimension ref="A1:G9"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A032A8F-582E-43C9-A3E7-5B4E9A57F508}">
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="8.69921875" customWidth="1"/>
@@ -1581,7 +1557,7 @@
     </row>
     <row r="4" spans="1:7" ht="234" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>26</v>
@@ -1604,7 +1580,7 @@
     </row>
     <row r="5" spans="1:7" ht="270" x14ac:dyDescent="0.45">
       <c r="A5" s="2" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>26</v>
@@ -1625,9 +1601,9 @@
         <v>31</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="306" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:7" ht="270" x14ac:dyDescent="0.45">
       <c r="A6" s="2" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>39</v>
@@ -1648,9 +1624,9 @@
         <v>31</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="324" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:7" ht="288" x14ac:dyDescent="0.45">
       <c r="A7" s="2" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>39</v>
@@ -1671,9 +1647,9 @@
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="288" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:7" ht="360" x14ac:dyDescent="0.45">
       <c r="A8" s="2" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>39</v>
@@ -1682,10 +1658,10 @@
         <v>44</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>30</v>
@@ -1694,38 +1670,15 @@
         <v>31</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="360" x14ac:dyDescent="0.45">
-      <c r="A9" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:G9" xr:uid="{5B4889EF-6408-405D-8680-A223B04F8382}"/>
+  <autoFilter ref="A1:G8" xr:uid="{0A032A8F-582E-43C9-A3E7-5B4E9A57F508}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6D56C1B-F250-4500-8B5A-07127B157EB4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53749C9D-2CC6-413B-9AAF-3B6AAAE9ECF6}">
   <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -1767,16 +1720,16 @@
         <v>26</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>28</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>31</v>
@@ -1790,16 +1743,16 @@
         <v>26</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>31</v>
@@ -1807,22 +1760,22 @@
     </row>
     <row r="4" spans="1:7" ht="126" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>26</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>28</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>31</v>
@@ -1830,22 +1783,22 @@
     </row>
     <row r="5" spans="1:7" ht="162" x14ac:dyDescent="0.45">
       <c r="A5" s="2" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>39</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>28</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>31</v>
@@ -1853,37 +1806,37 @@
     </row>
     <row r="6" spans="1:7" ht="216" x14ac:dyDescent="0.45">
       <c r="A6" s="2" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>39</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>28</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>31</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G6" xr:uid="{B6D56C1B-F250-4500-8B5A-07127B157EB4}"/>
+  <autoFilter ref="A1:G6" xr:uid="{53749C9D-2CC6-413B-9AAF-3B6AAAE9ECF6}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B4A2E79-1981-40C0-8F81-3581C5C7CB59}">
-  <dimension ref="A1:G14"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{708AA66F-7632-4316-BCD2-E802A96990B0}">
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="8.69921875" customWidth="1"/>
@@ -1916,7 +1869,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="409.6" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:7" ht="396" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
@@ -1924,16 +1877,16 @@
         <v>26</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>61</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>64</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>31</v>
@@ -1947,16 +1900,16 @@
         <v>26</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>31</v>
@@ -1970,16 +1923,16 @@
         <v>26</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>61</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>64</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>31</v>
@@ -1993,22 +1946,22 @@
         <v>26</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="324" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:7" ht="288" x14ac:dyDescent="0.45">
       <c r="A6" s="2" t="s">
         <v>8</v>
       </c>
@@ -2016,22 +1969,22 @@
         <v>26</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="D6" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="F6" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="E6" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>74</v>
-      </c>
       <c r="G6" s="2" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="378" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:7" ht="288" x14ac:dyDescent="0.45">
       <c r="A7" s="2" t="s">
         <v>15</v>
       </c>
@@ -2039,22 +1992,22 @@
         <v>26</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>77</v>
-      </c>
       <c r="F7" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="378" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:7" ht="288" x14ac:dyDescent="0.45">
       <c r="A8" s="2" t="s">
         <v>18</v>
       </c>
@@ -2062,22 +2015,22 @@
         <v>26</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>80</v>
-      </c>
       <c r="F8" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="378" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:7" ht="198" x14ac:dyDescent="0.45">
       <c r="A9" s="2" t="s">
         <v>5</v>
       </c>
@@ -2085,145 +2038,122 @@
         <v>26</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="144" x14ac:dyDescent="0.45">
+      <c r="A10" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="D10" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="F10" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="342" x14ac:dyDescent="0.45">
+      <c r="A11" s="2" t="s">
         <v>83</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="198" x14ac:dyDescent="0.45">
-      <c r="A10" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="144" x14ac:dyDescent="0.45">
-      <c r="A11" s="2" t="s">
-        <v>85</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>39</v>
       </c>
       <c r="C11" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="D11" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="E11" s="2" t="s">
+      <c r="F11" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="396" x14ac:dyDescent="0.45">
+      <c r="A12" s="2" t="s">
         <v>87</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="306" x14ac:dyDescent="0.45">
-      <c r="A12" s="2" t="s">
-        <v>88</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>39</v>
       </c>
       <c r="C12" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="378" x14ac:dyDescent="0.45">
+      <c r="A13" s="2" t="s">
         <v>89</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="396" x14ac:dyDescent="0.45">
-      <c r="A13" s="2" t="s">
-        <v>92</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>39</v>
       </c>
       <c r="C13" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="F13" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="D13" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>64</v>
-      </c>
       <c r="G13" s="2" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="378" x14ac:dyDescent="0.45">
-      <c r="A14" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:G14" xr:uid="{9B4A2E79-1981-40C0-8F81-3581C5C7CB59}"/>
+  <autoFilter ref="A1:G13" xr:uid="{708AA66F-7632-4316-BCD2-E802A96990B0}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{696268B0-D2E8-48C7-82C1-B2E767FCC236}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E05DC9B2-8128-4C5A-9AAF-0A40C17D4F5C}">
   <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -2265,16 +2195,16 @@
         <v>26</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>31</v>
@@ -2288,16 +2218,16 @@
         <v>26</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>31</v>
@@ -2311,16 +2241,16 @@
         <v>26</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>31</v>
@@ -2334,16 +2264,16 @@
         <v>26</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>31</v>
@@ -2357,30 +2287,30 @@
         <v>39</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>31</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G6" xr:uid="{696268B0-D2E8-48C7-82C1-B2E767FCC236}"/>
+  <autoFilter ref="A1:G6" xr:uid="{E05DC9B2-8128-4C5A-9AAF-0A40C17D4F5C}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A3B333B-F7D4-41E0-8E5A-5356CD146E58}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE5A2B18-B584-4055-B085-422EBCF73F6C}">
   <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -2422,16 +2352,16 @@
         <v>26</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>31</v>
@@ -2445,16 +2375,16 @@
         <v>26</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>31</v>
@@ -2471,28 +2401,28 @@
         <v>31</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>31</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G4" xr:uid="{3A3B333B-F7D4-41E0-8E5A-5356CD146E58}"/>
+  <autoFilter ref="A1:G4" xr:uid="{CE5A2B18-B584-4055-B085-422EBCF73F6C}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24C51438-C5C8-4633-83DD-AB8CAB450C2D}">
-  <dimension ref="A1:G38"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D0EF008-F2AD-4166-9664-BE94C7FB43C0}">
+  <dimension ref="A1:G37"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="8.69921875" customWidth="1"/>
@@ -2533,22 +2463,22 @@
         <v>26</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="288" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:7" ht="306" x14ac:dyDescent="0.45">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
@@ -2556,16 +2486,16 @@
         <v>26</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>128</v>
-      </c>
       <c r="F3" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>31</v>
@@ -2579,22 +2509,22 @@
         <v>26</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="234" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:7" ht="270" x14ac:dyDescent="0.45">
       <c r="A5" s="2" t="s">
         <v>12</v>
       </c>
@@ -2602,22 +2532,22 @@
         <v>26</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="270" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:7" ht="126" x14ac:dyDescent="0.45">
       <c r="A6" s="2" t="s">
         <v>8</v>
       </c>
@@ -2625,22 +2555,22 @@
         <v>26</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="E6" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="E6" s="2" t="s">
-        <v>135</v>
-      </c>
       <c r="F6" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="126" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:7" ht="180" x14ac:dyDescent="0.45">
       <c r="A7" s="2" t="s">
         <v>15</v>
       </c>
@@ -2648,22 +2578,22 @@
         <v>26</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>53</v>
+        <v>133</v>
       </c>
       <c r="D7" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="F7" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="E7" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>138</v>
-      </c>
       <c r="G7" s="2" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="180" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:7" ht="198" x14ac:dyDescent="0.45">
       <c r="A8" s="2" t="s">
         <v>18</v>
       </c>
@@ -2671,22 +2601,22 @@
         <v>26</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="F8" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="E8" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>142</v>
-      </c>
       <c r="G8" s="2" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="198" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:7" ht="144" x14ac:dyDescent="0.45">
       <c r="A9" s="2" t="s">
         <v>5</v>
       </c>
@@ -2694,114 +2624,114 @@
         <v>26</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="252" x14ac:dyDescent="0.45">
+      <c r="A10" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="D10" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="E10" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="F9" s="2" t="s">
+      <c r="F10" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="G9" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="144" x14ac:dyDescent="0.45">
-      <c r="A10" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="D10" s="2" t="s">
+      <c r="G10" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="234" x14ac:dyDescent="0.45">
+      <c r="A11" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="E10" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="F10" s="2" t="s">
+      <c r="D11" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="G10" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="270" x14ac:dyDescent="0.45">
-      <c r="A11" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C11" s="2" t="s">
+      <c r="E11" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="F11" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="198" x14ac:dyDescent="0.45">
+      <c r="A12" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="E11" s="2" t="s">
+      <c r="D12" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="F11" s="2" t="s">
+      <c r="E12" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="G11" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="252" x14ac:dyDescent="0.45">
-      <c r="A12" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C12" s="2" t="s">
+      <c r="F12" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="180" x14ac:dyDescent="0.45">
+      <c r="A13" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="D13" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="E12" s="2" t="s">
+      <c r="E13" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="F12" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="198" x14ac:dyDescent="0.45">
-      <c r="A13" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>158</v>
-      </c>
       <c r="F13" s="2" t="s">
-        <v>129</v>
+        <v>142</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="180" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:7" ht="198" x14ac:dyDescent="0.45">
       <c r="A14" s="2" t="s">
         <v>11</v>
       </c>
@@ -2809,16 +2739,16 @@
         <v>26</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>148</v>
+        <v>124</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>31</v>
@@ -2826,22 +2756,22 @@
     </row>
     <row r="15" spans="1:7" ht="198" x14ac:dyDescent="0.45">
       <c r="A15" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>165</v>
-      </c>
       <c r="F15" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>31</v>
@@ -2849,91 +2779,91 @@
     </row>
     <row r="16" spans="1:7" ht="198" x14ac:dyDescent="0.45">
       <c r="A16" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="B16" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C16" s="2" t="s">
+      <c r="F16" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="216" x14ac:dyDescent="0.45">
+      <c r="A17" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="D16" s="2" t="s">
+      <c r="B17" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C17" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="E16" s="2" t="s">
+      <c r="D17" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="F16" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="198" x14ac:dyDescent="0.45">
-      <c r="A17" s="2" t="s">
+      <c r="E17" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="B17" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C17" s="2" t="s">
+      <c r="F17" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="198" x14ac:dyDescent="0.45">
+      <c r="A18" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="D17" s="2" t="s">
+      <c r="B18" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C18" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="E17" s="2" t="s">
+      <c r="D18" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="F17" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" ht="216" x14ac:dyDescent="0.45">
-      <c r="A18" s="2" t="s">
+      <c r="E18" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="B18" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C18" s="2" t="s">
+      <c r="F18" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="216" x14ac:dyDescent="0.45">
+      <c r="A19" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="D18" s="2" t="s">
+      <c r="B19" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C19" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="E18" s="2" t="s">
+      <c r="D19" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="F18" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" ht="198" x14ac:dyDescent="0.45">
-      <c r="A19" s="2" t="s">
+      <c r="E19" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="B19" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>181</v>
-      </c>
       <c r="F19" s="2" t="s">
-        <v>148</v>
+        <v>124</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>31</v>
@@ -2941,206 +2871,206 @@
     </row>
     <row r="20" spans="1:7" ht="216" x14ac:dyDescent="0.45">
       <c r="A20" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="E20" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="B20" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C20" s="2" t="s">
+      <c r="F20" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="234" x14ac:dyDescent="0.45">
+      <c r="A21" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="D20" s="2" t="s">
+      <c r="B21" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C21" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="E20" s="2" t="s">
+      <c r="D21" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="F20" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" ht="216" x14ac:dyDescent="0.45">
-      <c r="A21" s="2" t="s">
+      <c r="E21" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="B21" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C21" s="2" t="s">
+      <c r="F21" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="198" x14ac:dyDescent="0.45">
+      <c r="A22" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="D21" s="2" t="s">
+      <c r="B22" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C22" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="E21" s="2" t="s">
+      <c r="D22" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="F21" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" ht="234" x14ac:dyDescent="0.45">
-      <c r="A22" s="2" t="s">
+      <c r="E22" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="B22" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C22" s="2" t="s">
+      <c r="F22" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="216" x14ac:dyDescent="0.45">
+      <c r="A23" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="D22" s="2" t="s">
+      <c r="B23" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C23" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="E22" s="2" t="s">
+      <c r="D23" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="F22" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" ht="198" x14ac:dyDescent="0.45">
-      <c r="A23" s="2" t="s">
+      <c r="E23" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="B23" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C23" s="2" t="s">
+      <c r="F23" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="198" x14ac:dyDescent="0.45">
+      <c r="A24" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="D23" s="2" t="s">
+      <c r="B24" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C24" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="E23" s="2" t="s">
+      <c r="D24" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="F23" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" ht="216" x14ac:dyDescent="0.45">
-      <c r="A24" s="2" t="s">
+      <c r="E24" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="B24" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C24" s="2" t="s">
+      <c r="F24" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="324" x14ac:dyDescent="0.45">
+      <c r="A25" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="D24" s="2" t="s">
+      <c r="B25" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C25" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="E24" s="2" t="s">
+      <c r="D25" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="F24" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" ht="198" x14ac:dyDescent="0.45">
-      <c r="A25" s="2" t="s">
+      <c r="E25" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="B25" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C25" s="2" t="s">
+      <c r="F25" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="198" x14ac:dyDescent="0.45">
+      <c r="A26" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="D25" s="2" t="s">
+      <c r="B26" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C26" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="E25" s="2" t="s">
+      <c r="D26" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="F25" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" ht="342" x14ac:dyDescent="0.45">
-      <c r="A26" s="2" t="s">
+      <c r="E26" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="B26" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C26" s="2" t="s">
+      <c r="F26" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="252" x14ac:dyDescent="0.45">
+      <c r="A27" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="D26" s="2" t="s">
+      <c r="B27" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C27" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="E26" s="2" t="s">
+      <c r="D27" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="F26" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" ht="198" x14ac:dyDescent="0.45">
-      <c r="A27" s="2" t="s">
+      <c r="E27" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="B27" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C27" s="2" t="s">
+      <c r="F27" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="198" x14ac:dyDescent="0.45">
+      <c r="A28" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="D27" s="2" t="s">
+      <c r="B28" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C28" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="E27" s="2" t="s">
+      <c r="D28" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="F27" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" ht="252" x14ac:dyDescent="0.45">
-      <c r="A28" s="2" t="s">
+      <c r="E28" s="2" t="s">
         <v>214</v>
       </c>
-      <c r="B28" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>217</v>
-      </c>
       <c r="F28" s="2" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>31</v>
@@ -3148,137 +3078,137 @@
     </row>
     <row r="29" spans="1:7" ht="198" x14ac:dyDescent="0.45">
       <c r="A29" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="216" x14ac:dyDescent="0.45">
+      <c r="A30" s="2" t="s">
         <v>218</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" ht="198" x14ac:dyDescent="0.45">
-      <c r="A30" s="2" t="s">
-        <v>222</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>39</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>223</v>
+        <v>50</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>124</v>
+        <v>219</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="31" spans="1:7" ht="216" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:7" ht="234" x14ac:dyDescent="0.45">
       <c r="A31" s="2" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>39</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>53</v>
+        <v>222</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="234" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:7" ht="252" x14ac:dyDescent="0.45">
       <c r="A32" s="2" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>39</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>230</v>
+        <v>126</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>231</v>
+        <v>217</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="33" spans="1:7" ht="270" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:7" ht="306" x14ac:dyDescent="0.45">
       <c r="A33" s="2" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>39</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="34" spans="1:7" ht="306" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:7" ht="234" x14ac:dyDescent="0.45">
       <c r="A34" s="2" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>39</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>140</v>
+        <v>232</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>31</v>
@@ -3286,105 +3216,82 @@
     </row>
     <row r="35" spans="1:7" ht="234" x14ac:dyDescent="0.45">
       <c r="A35" s="2" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>39</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="36" spans="1:7" ht="234" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:7" ht="198" x14ac:dyDescent="0.45">
       <c r="A36" s="2" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>39</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="D36" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="G36" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" ht="252" x14ac:dyDescent="0.45">
+      <c r="A37" s="2" t="s">
         <v>239</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="F36" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="G36" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" ht="198" x14ac:dyDescent="0.45">
-      <c r="A37" s="2" t="s">
-        <v>243</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>39</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>144</v>
+        <v>241</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="1:7" ht="252" x14ac:dyDescent="0.45">
-      <c r="A38" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="E38" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="F38" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="G38" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:G38" xr:uid="{24C51438-C5C8-4633-83DD-AB8CAB450C2D}"/>
+  <autoFilter ref="A1:G37" xr:uid="{9D0EF008-F2AD-4166-9664-BE94C7FB43C0}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F35AD59-A05A-42FC-BDBC-146184D11439}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79118172-5ABF-4C2F-99E2-9102F2920937}">
   <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -3426,22 +3333,22 @@
         <v>26</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>28</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="252" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:7" ht="126" x14ac:dyDescent="0.45">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
@@ -3449,16 +3356,16 @@
         <v>26</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>28</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>31</v>
@@ -3472,16 +3379,16 @@
         <v>26</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>31</v>
@@ -3495,23 +3402,23 @@
         <v>39</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>28</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>31</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G5" xr:uid="{9F35AD59-A05A-42FC-BDBC-146184D11439}"/>
+  <autoFilter ref="A1:G5" xr:uid="{79118172-5ABF-4C2F-99E2-9102F2920937}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
